--- a/26-2 Sports Day/타임라인_인원관리팀/2026 Sports Day 2. 타임라인 & 인원관리표.xlsx
+++ b/26-2 Sports Day/타임라인_인원관리팀/2026 Sports Day 2. 타임라인 & 인원관리표.xlsx
@@ -876,18 +876,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEA9999"/>
-        <bgColor rgb="FFEA9999"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB6D7A8"/>
-        <bgColor rgb="FFB6D7A8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB4A7D6"/>
         <bgColor rgb="FFB4A7D6"/>
       </patternFill>
@@ -942,6 +930,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB6D7A8"/>
+        <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD0E0E3"/>
         <bgColor rgb="FFD0E0E3"/>
       </patternFill>
@@ -950,6 +944,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFCFE2F3"/>
         <bgColor rgb="FFCFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA9999"/>
+        <bgColor rgb="FFEA9999"/>
       </patternFill>
     </fill>
   </fills>
@@ -1575,7 +1575,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="207">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1643,7 +1643,7 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
@@ -1662,7 +1662,7 @@
     </xf>
     <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="14" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
+      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
@@ -1676,30 +1676,27 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="19" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="20" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="21" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="21" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="22" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1708,36 +1705,39 @@
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="23" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="23" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="24" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="25" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="22" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="24" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="14" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="24" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="25" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="27" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="27" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="28" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="28" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="26" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1747,9 +1747,6 @@
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1771,10 +1768,10 @@
     <xf borderId="32" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="27" fillId="11" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="27" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="33" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="33" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -1786,10 +1783,10 @@
     <xf borderId="12" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="34" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="34" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="21" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="21" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="35" fillId="5" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1813,9 +1810,6 @@
     <xf borderId="36" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf borderId="37" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1825,19 +1819,19 @@
     <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="34" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="34" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="27" fillId="11" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="27" fillId="9" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="28" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="28" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="33" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="33" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="20" fillId="9" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="20" fillId="7" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="15" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1846,6 +1840,9 @@
     <xf borderId="29" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="8" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf borderId="18" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -1855,10 +1852,7 @@
     <xf borderId="22" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="20" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="14" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1867,25 +1861,25 @@
     <xf borderId="13" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="22" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="22" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="12" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="38" fillId="13" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="38" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1900,22 +1894,22 @@
     <xf borderId="22" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="23" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="23" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="22" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1930,7 +1924,7 @@
     <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="22" fillId="15" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="22" fillId="13" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="29" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1945,16 +1939,16 @@
     <xf borderId="13" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="27" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="27" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="16" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="8" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="19" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="16" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1963,7 +1957,7 @@
     <xf borderId="22" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="14" fillId="17" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="14" fillId="15" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="39" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1981,7 +1975,7 @@
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="17" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="14" fillId="15" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -1996,7 +1990,7 @@
     <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="14" fillId="16" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="14" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2017,7 +2011,7 @@
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="40" fillId="18" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="40" fillId="17" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="14" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -2050,7 +2044,7 @@
     <xf borderId="22" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="14" fillId="17" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="14" fillId="15" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyFont="1"/>
@@ -2060,17 +2054,17 @@
     <xf borderId="14" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="36" fillId="19" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="36" fillId="18" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="45" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="45" fillId="19" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="45" fillId="18" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="19" fillId="19" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="19" fillId="18" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="22" fillId="15" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="22" fillId="13" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="22" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2097,19 +2091,19 @@
     <xf borderId="47" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="48" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="48" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="39" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="5" fillId="16" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="35" fillId="4" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -2121,7 +2115,7 @@
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="14" fillId="17" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="14" fillId="15" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="22" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2136,13 +2130,13 @@
     <xf borderId="36" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="36" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="36" fillId="19" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="39" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="39" fillId="16" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="39" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="39" fillId="16" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="39" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2154,10 +2148,10 @@
     <xf borderId="29" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="29" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="29" fillId="19" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="19" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2582,7 +2576,7 @@
         <v>10</v>
       </c>
       <c r="K3" s="24">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="L3" s="25"/>
       <c r="M3" s="26"/>
@@ -2600,7 +2594,7 @@
         <v>11</v>
       </c>
       <c r="K4" s="31">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="L4" s="32"/>
       <c r="M4" s="1"/>
@@ -2623,7 +2617,7 @@
         <v>13</v>
       </c>
       <c r="K5" s="37">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="L5" s="38"/>
       <c r="M5" s="39"/>
@@ -2634,24 +2628,24 @@
       <c r="R5" s="42"/>
       <c r="S5" s="42"/>
       <c r="T5" s="42"/>
-      <c r="U5" s="43"/>
+      <c r="U5" s="39"/>
     </row>
     <row r="6">
-      <c r="B6" s="44"/>
+      <c r="B6" s="43"/>
       <c r="C6" s="29"/>
-      <c r="D6" s="45"/>
+      <c r="D6" s="44"/>
       <c r="E6" s="19"/>
       <c r="G6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="46" t="s">
+      <c r="H6" s="45" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="22"/>
-      <c r="J6" s="47" t="s">
+      <c r="J6" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="24">
+      <c r="K6" s="47">
         <v>12.0</v>
       </c>
       <c r="L6" s="32"/>
@@ -2677,7 +2671,7 @@
       <c r="J7" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="53">
         <v>4.0</v>
       </c>
       <c r="L7" s="32"/>
@@ -2687,8 +2681,8 @@
     </row>
     <row r="8">
       <c r="B8" s="48"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="55"/>
       <c r="E8" s="19"/>
       <c r="G8" s="51"/>
       <c r="H8" s="52"/>
@@ -2696,7 +2690,7 @@
       <c r="J8" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="53">
         <v>16.0</v>
       </c>
       <c r="L8" s="32"/>
@@ -2715,23 +2709,23 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
-      <c r="AC8" s="55"/>
-      <c r="AE8" s="56"/>
-      <c r="AF8" s="56"/>
-      <c r="AG8" s="56"/>
-      <c r="AH8" s="56"/>
-      <c r="AI8" s="56"/>
-      <c r="AJ8" s="56"/>
-      <c r="AK8" s="56"/>
-      <c r="AL8" s="56"/>
-      <c r="AM8" s="56"/>
-      <c r="AN8" s="56"/>
-      <c r="AO8" s="56"/>
-      <c r="AP8" s="56"/>
-      <c r="AQ8" s="56"/>
-      <c r="AR8" s="56"/>
-      <c r="AS8" s="56"/>
-      <c r="AT8" s="56"/>
+      <c r="AC8" s="56"/>
+      <c r="AE8" s="39"/>
+      <c r="AF8" s="39"/>
+      <c r="AG8" s="39"/>
+      <c r="AH8" s="39"/>
+      <c r="AI8" s="39"/>
+      <c r="AJ8" s="39"/>
+      <c r="AK8" s="39"/>
+      <c r="AL8" s="39"/>
+      <c r="AM8" s="39"/>
+      <c r="AN8" s="39"/>
+      <c r="AO8" s="39"/>
+      <c r="AP8" s="39"/>
+      <c r="AQ8" s="39"/>
+      <c r="AR8" s="39"/>
+      <c r="AS8" s="39"/>
+      <c r="AT8" s="39"/>
     </row>
     <row r="9">
       <c r="B9" s="57"/>
@@ -2745,11 +2739,11 @@
         <v>19</v>
       </c>
       <c r="K9" s="31">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L9" s="32"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="56"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="39"/>
     </row>
     <row r="10">
       <c r="B10" s="58"/>
@@ -2763,16 +2757,16 @@
         <v>20</v>
       </c>
       <c r="K10" s="37">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="L10" s="32"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="64"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="63"/>
     </row>
     <row r="11">
       <c r="B11" s="27"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="66"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="65"/>
       <c r="G11" s="34" t="s">
         <v>21</v>
       </c>
@@ -2780,13 +2774,13 @@
         <v>22</v>
       </c>
       <c r="I11" s="22"/>
-      <c r="J11" s="47" t="s">
+      <c r="J11" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="K11" s="67">
+      <c r="K11" s="66">
         <v>5.0</v>
       </c>
-      <c r="L11" s="56"/>
+      <c r="L11" s="39"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -2794,7 +2788,7 @@
       <c r="Q11" s="1"/>
     </row>
     <row r="12">
-      <c r="B12" s="68"/>
+      <c r="B12" s="67"/>
       <c r="C12" s="29"/>
       <c r="D12" s="60"/>
       <c r="G12" s="51"/>
@@ -2802,26 +2796,26 @@
       <c r="J12" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="69">
+      <c r="K12" s="68">
         <v>1.0</v>
       </c>
-      <c r="L12" s="63"/>
-      <c r="M12" s="56"/>
-      <c r="N12" s="56"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
     </row>
     <row r="13">
       <c r="B13" s="33"/>
-      <c r="C13" s="70"/>
+      <c r="C13" s="69"/>
       <c r="D13" s="60"/>
       <c r="G13" s="51"/>
       <c r="I13" s="22"/>
-      <c r="J13" s="47" t="s">
+      <c r="J13" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="67">
+      <c r="K13" s="66">
         <v>7.0</v>
       </c>
-      <c r="L13" s="56"/>
+      <c r="L13" s="39"/>
       <c r="M13" s="26"/>
       <c r="N13" s="26"/>
       <c r="O13" s="26"/>
@@ -2833,36 +2827,36 @@
       <c r="V13" s="26"/>
     </row>
     <row r="14">
-      <c r="B14" s="71"/>
+      <c r="B14" s="70"/>
       <c r="C14" s="59"/>
-      <c r="D14" s="72"/>
+      <c r="D14" s="71"/>
       <c r="G14" s="51"/>
       <c r="I14" s="22"/>
       <c r="J14" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="69">
+      <c r="K14" s="68">
         <v>1.0</v>
       </c>
       <c r="L14" s="32"/>
-      <c r="N14" s="73"/>
+      <c r="N14" s="72"/>
     </row>
     <row r="15">
       <c r="B15" s="48"/>
       <c r="C15" s="17"/>
-      <c r="D15" s="54"/>
+      <c r="D15" s="55"/>
       <c r="E15" s="19"/>
       <c r="G15" s="51"/>
       <c r="I15" s="22"/>
       <c r="J15" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="K15" s="67">
+      <c r="K15" s="66">
         <v>8.0</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-      <c r="N15" s="73"/>
+      <c r="N15" s="72"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
@@ -2871,30 +2865,30 @@
     </row>
     <row r="16">
       <c r="B16" s="33"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="75"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="74"/>
       <c r="E16" s="19"/>
       <c r="G16" s="51"/>
       <c r="I16" s="22"/>
       <c r="J16" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="K16" s="69">
+      <c r="K16" s="68">
         <v>1.0</v>
       </c>
       <c r="L16" s="32"/>
     </row>
     <row r="17">
-      <c r="B17" s="44"/>
-      <c r="C17" s="76"/>
-      <c r="D17" s="77"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="76"/>
       <c r="E17" s="19"/>
       <c r="G17" s="51"/>
       <c r="I17" s="22"/>
       <c r="J17" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K17" s="67">
+      <c r="K17" s="66">
         <v>5.0</v>
       </c>
       <c r="L17" s="1"/>
@@ -2913,150 +2907,150 @@
     <row r="18">
       <c r="B18" s="58"/>
       <c r="C18" s="29"/>
-      <c r="D18" s="72"/>
+      <c r="D18" s="71"/>
       <c r="G18" s="51"/>
       <c r="I18" s="22"/>
       <c r="J18" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="K18" s="69">
+      <c r="K18" s="68">
         <v>1.0</v>
       </c>
       <c r="L18" s="32"/>
     </row>
     <row r="19">
       <c r="B19" s="48"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="78"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="77"/>
       <c r="E19" s="19"/>
       <c r="G19" s="51"/>
       <c r="I19" s="22"/>
       <c r="J19" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="K19" s="56">
+      <c r="K19" s="39">
         <v>4.0</v>
       </c>
-      <c r="L19" s="79"/>
+      <c r="L19" s="78"/>
       <c r="M19" s="32"/>
       <c r="N19" s="32"/>
       <c r="O19" s="32"/>
     </row>
     <row r="20">
-      <c r="B20" s="68"/>
+      <c r="B20" s="67"/>
       <c r="C20" s="60"/>
       <c r="D20" s="29"/>
       <c r="G20" s="30"/>
       <c r="H20" s="35"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="80" t="s">
+      <c r="J20" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="K20" s="81">
+      <c r="K20" s="80">
         <v>2.0</v>
       </c>
-      <c r="L20" s="56"/>
-      <c r="M20" s="56"/>
-      <c r="N20" s="56"/>
-      <c r="O20" s="56"/>
-      <c r="P20" s="56"/>
-      <c r="Q20" s="56"/>
-      <c r="R20" s="56"/>
-      <c r="S20" s="56"/>
-      <c r="T20" s="56"/>
-      <c r="U20" s="56"/>
-      <c r="V20" s="56"/>
-      <c r="W20" s="56"/>
-      <c r="X20" s="56"/>
-      <c r="Y20" s="56"/>
-      <c r="Z20" s="56"/>
-      <c r="AA20" s="56"/>
-      <c r="AB20" s="56"/>
-      <c r="AC20" s="56"/>
-      <c r="AD20" s="56"/>
-      <c r="AE20" s="56"/>
-      <c r="AF20" s="56"/>
-      <c r="AG20" s="56"/>
-      <c r="AH20" s="56"/>
-      <c r="AI20" s="56"/>
-      <c r="AJ20" s="56"/>
-      <c r="AK20" s="56"/>
-      <c r="AL20" s="56"/>
-      <c r="AM20" s="56"/>
-      <c r="AN20" s="56"/>
-      <c r="AO20" s="56"/>
-      <c r="AP20" s="56"/>
-      <c r="AQ20" s="56"/>
-      <c r="AR20" s="56"/>
-      <c r="AS20" s="56"/>
-      <c r="AT20" s="56"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="39"/>
+      <c r="R20" s="39"/>
+      <c r="S20" s="39"/>
+      <c r="T20" s="39"/>
+      <c r="U20" s="39"/>
+      <c r="V20" s="39"/>
+      <c r="W20" s="39"/>
+      <c r="X20" s="39"/>
+      <c r="Y20" s="39"/>
+      <c r="Z20" s="39"/>
+      <c r="AA20" s="39"/>
+      <c r="AB20" s="39"/>
+      <c r="AC20" s="39"/>
+      <c r="AD20" s="39"/>
+      <c r="AE20" s="39"/>
+      <c r="AF20" s="39"/>
+      <c r="AG20" s="39"/>
+      <c r="AH20" s="39"/>
+      <c r="AI20" s="39"/>
+      <c r="AJ20" s="39"/>
+      <c r="AK20" s="39"/>
+      <c r="AL20" s="39"/>
+      <c r="AM20" s="39"/>
+      <c r="AN20" s="39"/>
+      <c r="AO20" s="39"/>
+      <c r="AP20" s="39"/>
+      <c r="AQ20" s="39"/>
+      <c r="AR20" s="39"/>
+      <c r="AS20" s="39"/>
+      <c r="AT20" s="39"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="27"/>
       <c r="C21" s="17"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="83"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="82"/>
       <c r="G21" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="46" t="s">
+      <c r="H21" s="45" t="s">
         <v>34</v>
       </c>
       <c r="I21" s="22"/>
-      <c r="J21" s="84" t="s">
+      <c r="J21" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="K21" s="24">
+      <c r="K21" s="47">
         <v>10.0</v>
       </c>
-      <c r="L21" s="85"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="56"/>
-      <c r="O21" s="56"/>
-      <c r="P21" s="85"/>
-      <c r="Q21" s="56"/>
-      <c r="R21" s="56"/>
-      <c r="S21" s="56"/>
-      <c r="T21" s="56"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="39"/>
+      <c r="T21" s="39"/>
       <c r="U21" s="1"/>
-      <c r="AM21" s="56"/>
-      <c r="AN21" s="56"/>
-      <c r="AO21" s="56"/>
-      <c r="AP21" s="56"/>
-      <c r="AQ21" s="56"/>
-      <c r="AR21" s="56"/>
-      <c r="AS21" s="56"/>
-      <c r="AT21" s="56"/>
+      <c r="AM21" s="39"/>
+      <c r="AN21" s="39"/>
+      <c r="AO21" s="39"/>
+      <c r="AP21" s="39"/>
+      <c r="AQ21" s="39"/>
+      <c r="AR21" s="39"/>
+      <c r="AS21" s="39"/>
+      <c r="AT21" s="39"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="B22" s="68"/>
+      <c r="B22" s="67"/>
       <c r="C22" s="29"/>
-      <c r="D22" s="86"/>
+      <c r="D22" s="84"/>
       <c r="G22" s="51"/>
       <c r="H22" s="52"/>
       <c r="I22" s="22"/>
-      <c r="J22" s="87" t="s">
+      <c r="J22" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="53">
         <v>2.0</v>
       </c>
-      <c r="L22" s="73"/>
-      <c r="M22" s="73"/>
-      <c r="N22" s="73"/>
-      <c r="O22" s="73"/>
-      <c r="P22" s="88"/>
-      <c r="Q22" s="88"/>
-      <c r="R22" s="88"/>
-      <c r="S22" s="88"/>
-      <c r="AM22" s="56"/>
-      <c r="AN22" s="56"/>
-      <c r="AO22" s="56"/>
-      <c r="AP22" s="56"/>
-      <c r="AQ22" s="56"/>
-      <c r="AR22" s="56"/>
-      <c r="AS22" s="56"/>
-      <c r="AT22" s="56"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="86"/>
+      <c r="Q22" s="86"/>
+      <c r="R22" s="86"/>
+      <c r="S22" s="86"/>
+      <c r="AM22" s="39"/>
+      <c r="AN22" s="39"/>
+      <c r="AO22" s="39"/>
+      <c r="AP22" s="39"/>
+      <c r="AQ22" s="39"/>
+      <c r="AR22" s="39"/>
+      <c r="AS22" s="39"/>
+      <c r="AT22" s="39"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="57"/>
@@ -3065,159 +3059,159 @@
       <c r="G23" s="51"/>
       <c r="H23" s="52"/>
       <c r="I23" s="22"/>
-      <c r="J23" s="87" t="s">
+      <c r="J23" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="K23" s="31">
+      <c r="K23" s="53">
         <v>2.0</v>
       </c>
-      <c r="L23" s="73"/>
-      <c r="M23" s="73"/>
-      <c r="N23" s="73"/>
-      <c r="O23" s="73"/>
-      <c r="P23" s="88"/>
-      <c r="Q23" s="88"/>
-      <c r="R23" s="88"/>
-      <c r="S23" s="88"/>
-      <c r="AM23" s="56"/>
-      <c r="AN23" s="56"/>
-      <c r="AO23" s="56"/>
-      <c r="AP23" s="56"/>
-      <c r="AQ23" s="56"/>
-      <c r="AR23" s="56"/>
-      <c r="AS23" s="56"/>
-      <c r="AT23" s="56"/>
+      <c r="L23" s="72"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="86"/>
+      <c r="Q23" s="86"/>
+      <c r="R23" s="86"/>
+      <c r="S23" s="86"/>
+      <c r="AM23" s="39"/>
+      <c r="AN23" s="39"/>
+      <c r="AO23" s="39"/>
+      <c r="AP23" s="39"/>
+      <c r="AQ23" s="39"/>
+      <c r="AR23" s="39"/>
+      <c r="AS23" s="39"/>
+      <c r="AT23" s="39"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="B24" s="44"/>
-      <c r="C24" s="89"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="87"/>
       <c r="D24" s="29"/>
       <c r="G24" s="51"/>
       <c r="H24" s="52"/>
       <c r="I24" s="22"/>
-      <c r="J24" s="87" t="s">
+      <c r="J24" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="53">
         <v>3.0</v>
       </c>
-      <c r="L24" s="73"/>
-      <c r="M24" s="73"/>
-      <c r="N24" s="73"/>
-      <c r="O24" s="73"/>
-      <c r="P24" s="88"/>
-      <c r="Q24" s="88"/>
-      <c r="R24" s="88"/>
-      <c r="S24" s="88"/>
-      <c r="AM24" s="56"/>
-      <c r="AN24" s="56"/>
-      <c r="AO24" s="56"/>
-      <c r="AP24" s="56"/>
-      <c r="AQ24" s="56"/>
-      <c r="AR24" s="56"/>
-      <c r="AS24" s="56"/>
-      <c r="AT24" s="56"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="72"/>
+      <c r="P24" s="86"/>
+      <c r="Q24" s="86"/>
+      <c r="R24" s="86"/>
+      <c r="S24" s="86"/>
+      <c r="AM24" s="39"/>
+      <c r="AN24" s="39"/>
+      <c r="AO24" s="39"/>
+      <c r="AP24" s="39"/>
+      <c r="AQ24" s="39"/>
+      <c r="AR24" s="39"/>
+      <c r="AS24" s="39"/>
+      <c r="AT24" s="39"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="B25" s="90"/>
-      <c r="C25" s="91"/>
-      <c r="D25" s="92"/>
-      <c r="E25" s="83"/>
+      <c r="B25" s="88"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="82"/>
       <c r="G25" s="51"/>
       <c r="H25" s="52"/>
       <c r="I25" s="22"/>
-      <c r="J25" s="87" t="s">
+      <c r="J25" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="53">
         <v>3.0</v>
       </c>
-      <c r="L25" s="56"/>
-      <c r="M25" s="56"/>
-      <c r="N25" s="56"/>
-      <c r="O25" s="88"/>
-      <c r="P25" s="88"/>
-      <c r="Q25" s="88"/>
-      <c r="R25" s="88"/>
-      <c r="S25" s="88"/>
-      <c r="AM25" s="56"/>
-      <c r="AN25" s="56"/>
-      <c r="AO25" s="56"/>
-      <c r="AP25" s="56"/>
-      <c r="AQ25" s="56"/>
-      <c r="AR25" s="56"/>
-      <c r="AS25" s="56"/>
-      <c r="AT25" s="56"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="86"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="86"/>
+      <c r="R25" s="86"/>
+      <c r="S25" s="86"/>
+      <c r="AM25" s="39"/>
+      <c r="AN25" s="39"/>
+      <c r="AO25" s="39"/>
+      <c r="AP25" s="39"/>
+      <c r="AQ25" s="39"/>
+      <c r="AR25" s="39"/>
+      <c r="AS25" s="39"/>
+      <c r="AT25" s="39"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="B26" s="93"/>
-      <c r="C26" s="89"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="87"/>
       <c r="D26" s="60"/>
-      <c r="E26" s="83"/>
+      <c r="E26" s="82"/>
       <c r="G26" s="51"/>
       <c r="H26" s="52"/>
       <c r="I26" s="22"/>
-      <c r="J26" s="87" t="s">
+      <c r="J26" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="K26" s="31">
+      <c r="K26" s="53">
         <v>2.0</v>
       </c>
-      <c r="L26" s="56"/>
-      <c r="M26" s="56"/>
-      <c r="N26" s="56"/>
-      <c r="O26" s="56"/>
-      <c r="P26" s="56"/>
-      <c r="Q26" s="56"/>
-      <c r="R26" s="56"/>
-      <c r="S26" s="56"/>
-      <c r="T26" s="56"/>
-      <c r="U26" s="56"/>
-      <c r="V26" s="56"/>
-      <c r="W26" s="56"/>
-      <c r="X26" s="56"/>
-      <c r="Y26" s="56"/>
-      <c r="Z26" s="56"/>
-      <c r="AA26" s="56"/>
-      <c r="AB26" s="56"/>
-      <c r="AC26" s="56"/>
-      <c r="AD26" s="56"/>
-      <c r="AE26" s="56"/>
-      <c r="AF26" s="56"/>
-      <c r="AG26" s="56"/>
-      <c r="AH26" s="56"/>
-      <c r="AI26" s="56"/>
-      <c r="AJ26" s="56"/>
-      <c r="AK26" s="56"/>
-      <c r="AL26" s="56"/>
-      <c r="AM26" s="56"/>
-      <c r="AN26" s="56"/>
-      <c r="AO26" s="56"/>
-      <c r="AP26" s="56"/>
-      <c r="AQ26" s="56"/>
-      <c r="AR26" s="56"/>
-      <c r="AS26" s="56"/>
-      <c r="AT26" s="56"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
+      <c r="S26" s="39"/>
+      <c r="T26" s="39"/>
+      <c r="U26" s="39"/>
+      <c r="V26" s="39"/>
+      <c r="W26" s="39"/>
+      <c r="X26" s="39"/>
+      <c r="Y26" s="39"/>
+      <c r="Z26" s="39"/>
+      <c r="AA26" s="39"/>
+      <c r="AB26" s="39"/>
+      <c r="AC26" s="39"/>
+      <c r="AD26" s="39"/>
+      <c r="AE26" s="39"/>
+      <c r="AF26" s="39"/>
+      <c r="AG26" s="39"/>
+      <c r="AH26" s="39"/>
+      <c r="AI26" s="39"/>
+      <c r="AJ26" s="39"/>
+      <c r="AK26" s="39"/>
+      <c r="AL26" s="39"/>
+      <c r="AM26" s="39"/>
+      <c r="AN26" s="39"/>
+      <c r="AO26" s="39"/>
+      <c r="AP26" s="39"/>
+      <c r="AQ26" s="39"/>
+      <c r="AR26" s="39"/>
+      <c r="AS26" s="39"/>
+      <c r="AT26" s="39"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="B27" s="94"/>
-      <c r="C27" s="65"/>
+      <c r="B27" s="92"/>
+      <c r="C27" s="64"/>
       <c r="D27" s="60"/>
-      <c r="E27" s="83"/>
+      <c r="E27" s="82"/>
       <c r="G27" s="30"/>
       <c r="H27" s="61"/>
       <c r="I27" s="36"/>
-      <c r="J27" s="95" t="s">
+      <c r="J27" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="K27" s="37">
+      <c r="K27" s="94">
         <v>24.0</v>
       </c>
-      <c r="L27" s="56"/>
-      <c r="M27" s="56"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="56"/>
-      <c r="P27" s="56"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="39"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
@@ -3225,78 +3219,78 @@
       <c r="U27" s="1"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="B28" s="96"/>
-      <c r="C28" s="74"/>
+      <c r="B28" s="95"/>
+      <c r="C28" s="73"/>
       <c r="D28" s="60"/>
-      <c r="E28" s="83"/>
+      <c r="E28" s="82"/>
       <c r="G28" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="H28" s="46" t="s">
+      <c r="H28" s="45" t="s">
         <v>43</v>
       </c>
       <c r="I28" s="22"/>
-      <c r="J28" s="87" t="s">
+      <c r="J28" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="K28" s="97">
+      <c r="K28" s="96">
         <v>4.0</v>
       </c>
-      <c r="L28" s="98"/>
-      <c r="M28" s="99"/>
-      <c r="N28" s="99"/>
-      <c r="O28" s="99"/>
-      <c r="P28" s="99"/>
-      <c r="Q28" s="99"/>
-      <c r="R28" s="99"/>
-      <c r="S28" s="99"/>
-      <c r="T28" s="99"/>
-      <c r="U28" s="99"/>
-      <c r="V28" s="99"/>
+      <c r="L28" s="97"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="42"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="42"/>
+      <c r="S28" s="42"/>
+      <c r="T28" s="42"/>
+      <c r="U28" s="42"/>
+      <c r="V28" s="42"/>
       <c r="W28" s="26"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="B29" s="100"/>
-      <c r="C29" s="76"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="75"/>
       <c r="D29" s="17"/>
-      <c r="E29" s="83"/>
+      <c r="E29" s="82"/>
       <c r="G29" s="51"/>
       <c r="H29" s="52"/>
       <c r="I29" s="22"/>
-      <c r="J29" s="101" t="s">
+      <c r="J29" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="K29" s="102">
+      <c r="K29" s="100">
         <v>10.0</v>
       </c>
-      <c r="L29" s="103"/>
-      <c r="M29" s="104"/>
-      <c r="N29" s="105"/>
-      <c r="O29" s="105"/>
-      <c r="P29" s="106"/>
-      <c r="Q29" s="106"/>
-      <c r="R29" s="107"/>
-      <c r="S29" s="107"/>
-      <c r="T29" s="108"/>
-      <c r="U29" s="108"/>
+      <c r="L29" s="101"/>
+      <c r="M29" s="102"/>
+      <c r="N29" s="103"/>
+      <c r="O29" s="103"/>
+      <c r="P29" s="104"/>
+      <c r="Q29" s="104"/>
+      <c r="R29" s="105"/>
+      <c r="S29" s="105"/>
+      <c r="T29" s="106"/>
+      <c r="U29" s="106"/>
       <c r="V29" s="26"/>
       <c r="W29" s="26"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="B30" s="109"/>
+      <c r="B30" s="107"/>
       <c r="C30" s="29"/>
       <c r="D30" s="50"/>
-      <c r="E30" s="83"/>
+      <c r="E30" s="82"/>
       <c r="G30" s="30"/>
       <c r="H30" s="61"/>
       <c r="I30" s="36"/>
-      <c r="J30" s="110" t="s">
+      <c r="J30" s="108" t="s">
         <v>46</v>
       </c>
-      <c r="K30" s="111">
+      <c r="K30" s="109">
         <v>33.0</v>
       </c>
-      <c r="L30" s="98"/>
+      <c r="L30" s="97"/>
       <c r="M30" s="26"/>
       <c r="N30" s="26"/>
       <c r="O30" s="26"/>
@@ -3309,97 +3303,97 @@
       <c r="V30" s="26"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="B31" s="100"/>
+      <c r="B31" s="98"/>
       <c r="C31" s="17"/>
-      <c r="D31" s="77"/>
-      <c r="E31" s="83"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="82"/>
       <c r="G31" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="H31" s="46" t="s">
+      <c r="H31" s="45" t="s">
         <v>48</v>
       </c>
       <c r="I31" s="22"/>
       <c r="J31" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="K31" s="112">
+      <c r="K31" s="110">
         <v>2.0</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="B32" s="96"/>
-      <c r="C32" s="74"/>
-      <c r="D32" s="75"/>
+      <c r="B32" s="95"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="74"/>
       <c r="G32" s="51"/>
       <c r="H32" s="52"/>
       <c r="I32" s="22"/>
       <c r="J32" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="K32" s="112">
+      <c r="K32" s="110">
         <v>2.0</v>
       </c>
-      <c r="L32" s="113"/>
+      <c r="L32" s="111"/>
       <c r="M32" s="1"/>
       <c r="R32" s="1"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="B33" s="100"/>
-      <c r="C33" s="76"/>
-      <c r="D33" s="78"/>
+      <c r="B33" s="98"/>
+      <c r="C33" s="75"/>
+      <c r="D33" s="77"/>
       <c r="G33" s="51"/>
       <c r="H33" s="52"/>
       <c r="I33" s="22"/>
       <c r="J33" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="K33" s="112">
+      <c r="K33" s="110">
         <v>5.0</v>
       </c>
-      <c r="L33" s="114"/>
-      <c r="M33" s="115"/>
-      <c r="N33" s="116"/>
-      <c r="O33" s="117"/>
-      <c r="P33" s="118"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="113"/>
+      <c r="N33" s="114"/>
+      <c r="O33" s="115"/>
+      <c r="P33" s="116"/>
       <c r="R33" s="1"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="B34" s="94"/>
+      <c r="B34" s="92"/>
       <c r="C34" s="29"/>
-      <c r="D34" s="66"/>
-      <c r="E34" s="83"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="82"/>
       <c r="G34" s="51"/>
       <c r="H34" s="52"/>
       <c r="I34" s="22"/>
       <c r="J34" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="K34" s="112">
+      <c r="K34" s="110">
         <v>2.0</v>
       </c>
-      <c r="L34" s="113"/>
+      <c r="L34" s="111"/>
       <c r="M34" s="1"/>
       <c r="R34" s="1"/>
       <c r="V34" s="1"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="B35" s="119"/>
+      <c r="B35" s="117"/>
       <c r="C35" s="49"/>
       <c r="D35" s="17"/>
-      <c r="E35" s="83"/>
+      <c r="E35" s="82"/>
       <c r="G35" s="51"/>
       <c r="H35" s="52"/>
       <c r="I35" s="22"/>
       <c r="J35" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="K35" s="112">
+      <c r="K35" s="110">
         <v>2.0</v>
       </c>
-      <c r="L35" s="120"/>
+      <c r="L35" s="118"/>
       <c r="M35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
@@ -3409,20 +3403,20 @@
       <c r="W35" s="1"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="B36" s="100"/>
+      <c r="B36" s="98"/>
       <c r="C36" s="29"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="83"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="82"/>
       <c r="G36" s="51"/>
       <c r="H36" s="52"/>
       <c r="I36" s="22"/>
       <c r="J36" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="K36" s="112">
+      <c r="K36" s="110">
         <v>5.0</v>
       </c>
-      <c r="L36" s="73"/>
+      <c r="L36" s="72"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
@@ -3435,100 +3429,100 @@
       <c r="W36" s="1"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="B37" s="119"/>
+      <c r="B37" s="117"/>
       <c r="C37" s="49"/>
       <c r="D37" s="17"/>
-      <c r="E37" s="83"/>
+      <c r="E37" s="82"/>
       <c r="G37" s="30"/>
       <c r="H37" s="61"/>
       <c r="I37" s="36"/>
       <c r="J37" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="K37" s="121">
+      <c r="K37" s="119">
         <v>29.0</v>
       </c>
-      <c r="L37" s="122"/>
-      <c r="M37" s="122"/>
-      <c r="N37" s="122"/>
-      <c r="O37" s="123"/>
-      <c r="P37" s="123"/>
-      <c r="Q37" s="122"/>
-      <c r="R37" s="122"/>
-      <c r="S37" s="122"/>
-      <c r="T37" s="122"/>
-      <c r="U37" s="122"/>
-      <c r="V37" s="122"/>
-      <c r="W37" s="122"/>
-      <c r="X37" s="122"/>
-      <c r="Y37" s="122"/>
-      <c r="Z37" s="122"/>
-      <c r="AA37" s="122"/>
-      <c r="AB37" s="122"/>
+      <c r="L37" s="120"/>
+      <c r="M37" s="120"/>
+      <c r="N37" s="120"/>
+      <c r="O37" s="121"/>
+      <c r="P37" s="121"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="120"/>
+      <c r="S37" s="120"/>
+      <c r="T37" s="120"/>
+      <c r="U37" s="120"/>
+      <c r="V37" s="120"/>
+      <c r="W37" s="120"/>
+      <c r="X37" s="120"/>
+      <c r="Y37" s="120"/>
+      <c r="Z37" s="120"/>
+      <c r="AA37" s="120"/>
+      <c r="AB37" s="120"/>
     </row>
     <row r="38">
-      <c r="B38" s="96"/>
-      <c r="C38" s="74"/>
+      <c r="B38" s="95"/>
+      <c r="C38" s="73"/>
       <c r="D38" s="29"/>
-      <c r="E38" s="83"/>
-      <c r="G38" s="46" t="s">
+      <c r="E38" s="82"/>
+      <c r="G38" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="H38" s="124" t="s">
+      <c r="H38" s="122" t="s">
         <v>57</v>
       </c>
       <c r="I38" s="22"/>
-      <c r="J38" s="125" t="s">
+      <c r="J38" s="123" t="s">
         <v>58</v>
       </c>
       <c r="K38" s="36"/>
-      <c r="L38" s="122"/>
-      <c r="M38" s="122"/>
-      <c r="N38" s="122"/>
-      <c r="O38" s="122"/>
-      <c r="P38" s="122"/>
-      <c r="Q38" s="122"/>
-      <c r="R38" s="122"/>
-      <c r="S38" s="122"/>
-      <c r="T38" s="122"/>
-      <c r="U38" s="122"/>
-      <c r="V38" s="122"/>
-      <c r="W38" s="122"/>
-      <c r="X38" s="122"/>
-      <c r="Y38" s="122"/>
-      <c r="Z38" s="122"/>
-      <c r="AA38" s="122"/>
-      <c r="AB38" s="122"/>
+      <c r="L38" s="120"/>
+      <c r="M38" s="120"/>
+      <c r="N38" s="120"/>
+      <c r="O38" s="120"/>
+      <c r="P38" s="120"/>
+      <c r="Q38" s="120"/>
+      <c r="R38" s="120"/>
+      <c r="S38" s="120"/>
+      <c r="T38" s="120"/>
+      <c r="U38" s="120"/>
+      <c r="V38" s="120"/>
+      <c r="W38" s="120"/>
+      <c r="X38" s="120"/>
+      <c r="Y38" s="120"/>
+      <c r="Z38" s="120"/>
+      <c r="AA38" s="120"/>
+      <c r="AB38" s="120"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="B39" s="109"/>
-      <c r="C39" s="65"/>
+      <c r="B39" s="107"/>
+      <c r="C39" s="64"/>
       <c r="D39" s="17"/>
-      <c r="E39" s="126"/>
+      <c r="E39" s="124"/>
       <c r="G39" s="52"/>
       <c r="H39" s="52"/>
       <c r="I39" s="22"/>
-      <c r="J39" s="127" t="s">
+      <c r="J39" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="K39" s="128">
+      <c r="K39" s="126">
         <v>2.0</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="B40" s="129"/>
-      <c r="C40" s="91"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="83"/>
+      <c r="B40" s="127"/>
+      <c r="C40" s="89"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="82"/>
       <c r="G40" s="52"/>
       <c r="H40" s="52"/>
       <c r="I40" s="22"/>
       <c r="J40" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="K40" s="128">
+      <c r="K40" s="126">
         <v>3.0</v>
       </c>
       <c r="L40" s="1"/>
@@ -3536,17 +3530,17 @@
       <c r="N40" s="1"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="B41" s="129"/>
-      <c r="C41" s="91"/>
-      <c r="D41" s="92"/>
-      <c r="E41" s="83"/>
+      <c r="B41" s="127"/>
+      <c r="C41" s="89"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="82"/>
       <c r="G41" s="52"/>
       <c r="H41" s="52"/>
       <c r="I41" s="22"/>
       <c r="J41" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="K41" s="128">
+      <c r="K41" s="126">
         <v>2.0</v>
       </c>
       <c r="L41" s="1"/>
@@ -3557,342 +3551,342 @@
       <c r="R41" s="1"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="B42" s="129"/>
+      <c r="B42" s="127"/>
       <c r="C42" s="29"/>
-      <c r="D42" s="92"/>
-      <c r="E42" s="83"/>
+      <c r="D42" s="90"/>
+      <c r="E42" s="82"/>
       <c r="G42" s="52"/>
       <c r="H42" s="61"/>
       <c r="I42" s="36"/>
-      <c r="J42" s="130" t="s">
+      <c r="J42" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="K42" s="131">
+      <c r="K42" s="129">
         <v>2.0</v>
       </c>
-      <c r="L42" s="122"/>
-      <c r="M42" s="132"/>
-      <c r="N42" s="133"/>
-      <c r="O42" s="122"/>
-      <c r="P42" s="122"/>
-      <c r="Q42" s="122"/>
-      <c r="R42" s="122"/>
-      <c r="S42" s="122"/>
-      <c r="T42" s="122"/>
-      <c r="U42" s="122"/>
-      <c r="V42" s="122"/>
-      <c r="W42" s="122"/>
-      <c r="X42" s="122"/>
-      <c r="Y42" s="122"/>
-      <c r="Z42" s="122"/>
-      <c r="AA42" s="122"/>
-      <c r="AB42" s="122"/>
+      <c r="L42" s="120"/>
+      <c r="M42" s="130"/>
+      <c r="N42" s="131"/>
+      <c r="O42" s="120"/>
+      <c r="P42" s="120"/>
+      <c r="Q42" s="120"/>
+      <c r="R42" s="120"/>
+      <c r="S42" s="120"/>
+      <c r="T42" s="120"/>
+      <c r="U42" s="120"/>
+      <c r="V42" s="120"/>
+      <c r="W42" s="120"/>
+      <c r="X42" s="120"/>
+      <c r="Y42" s="120"/>
+      <c r="Z42" s="120"/>
+      <c r="AA42" s="120"/>
+      <c r="AB42" s="120"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="B43" s="94"/>
+      <c r="B43" s="92"/>
       <c r="C43" s="17"/>
-      <c r="D43" s="66"/>
-      <c r="E43" s="83"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="82"/>
       <c r="G43" s="52"/>
-      <c r="H43" s="134" t="s">
+      <c r="H43" s="132" t="s">
         <v>63</v>
       </c>
-      <c r="I43" s="135" t="s">
+      <c r="I43" s="133" t="s">
         <v>64</v>
       </c>
       <c r="J43" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="K43" s="112">
+      <c r="K43" s="110">
         <v>1.0</v>
       </c>
-      <c r="L43" s="56"/>
+      <c r="L43" s="39"/>
       <c r="M43" s="1"/>
-      <c r="N43" s="136"/>
+      <c r="N43" s="134"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="B44" s="119"/>
+      <c r="B44" s="117"/>
       <c r="C44" s="29"/>
       <c r="D44" s="50"/>
-      <c r="E44" s="83"/>
+      <c r="E44" s="82"/>
       <c r="G44" s="52"/>
       <c r="H44" s="52"/>
       <c r="I44" s="51"/>
-      <c r="J44" s="137" t="s">
+      <c r="J44" s="135" t="s">
         <v>66</v>
       </c>
-      <c r="K44" s="138">
+      <c r="K44" s="136">
         <v>6.0</v>
       </c>
-      <c r="L44" s="114"/>
-      <c r="M44" s="115"/>
-      <c r="N44" s="116"/>
-      <c r="O44" s="117"/>
-      <c r="P44" s="118"/>
+      <c r="L44" s="112"/>
+      <c r="M44" s="113"/>
+      <c r="N44" s="114"/>
+      <c r="O44" s="115"/>
+      <c r="P44" s="116"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="B45" s="119"/>
+      <c r="B45" s="117"/>
       <c r="C45" s="17"/>
       <c r="D45" s="50"/>
-      <c r="E45" s="83"/>
+      <c r="E45" s="82"/>
       <c r="G45" s="52"/>
       <c r="H45" s="52"/>
       <c r="I45" s="51"/>
       <c r="J45" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="K45" s="112">
+      <c r="K45" s="110">
         <v>2.0</v>
       </c>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="B46" s="96"/>
-      <c r="C46" s="139"/>
-      <c r="D46" s="75"/>
-      <c r="E46" s="83"/>
+      <c r="B46" s="95"/>
+      <c r="C46" s="137"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="82"/>
       <c r="G46" s="52"/>
       <c r="H46" s="52"/>
       <c r="I46" s="51"/>
       <c r="J46" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="K46" s="112">
+      <c r="K46" s="110">
         <v>2.0</v>
       </c>
-      <c r="L46" s="63"/>
+      <c r="L46" s="38"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="B47" s="100"/>
+      <c r="B47" s="98"/>
       <c r="C47" s="17"/>
-      <c r="D47" s="77"/>
-      <c r="E47" s="126"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="124"/>
       <c r="G47" s="52"/>
       <c r="H47" s="52"/>
       <c r="I47" s="30"/>
       <c r="J47" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="K47" s="121">
+      <c r="K47" s="119">
         <v>4.0</v>
       </c>
-      <c r="L47" s="140"/>
-      <c r="M47" s="122"/>
-      <c r="N47" s="122"/>
-      <c r="O47" s="123"/>
-      <c r="P47" s="122"/>
-      <c r="Q47" s="122"/>
-      <c r="R47" s="122"/>
-      <c r="S47" s="122"/>
-      <c r="T47" s="122"/>
-      <c r="U47" s="122"/>
-      <c r="V47" s="122"/>
-      <c r="W47" s="122"/>
-      <c r="X47" s="122"/>
-      <c r="Y47" s="122"/>
-      <c r="Z47" s="122"/>
-      <c r="AA47" s="122"/>
-      <c r="AB47" s="122"/>
+      <c r="L47" s="138"/>
+      <c r="M47" s="120"/>
+      <c r="N47" s="120"/>
+      <c r="O47" s="121"/>
+      <c r="P47" s="120"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="120"/>
+      <c r="S47" s="120"/>
+      <c r="T47" s="120"/>
+      <c r="U47" s="120"/>
+      <c r="V47" s="120"/>
+      <c r="W47" s="120"/>
+      <c r="X47" s="120"/>
+      <c r="Y47" s="120"/>
+      <c r="Z47" s="120"/>
+      <c r="AA47" s="120"/>
+      <c r="AB47" s="120"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="B48" s="94"/>
+      <c r="B48" s="92"/>
       <c r="C48" s="29"/>
-      <c r="D48" s="66"/>
-      <c r="E48" s="83"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="82"/>
       <c r="G48" s="52"/>
       <c r="H48" s="52"/>
-      <c r="I48" s="141" t="s">
+      <c r="I48" s="139" t="s">
         <v>70</v>
       </c>
       <c r="J48" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="K48" s="112">
+      <c r="K48" s="110">
         <v>1.0</v>
       </c>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="B49" s="94"/>
+      <c r="B49" s="92"/>
       <c r="C49" s="17"/>
-      <c r="D49" s="66"/>
-      <c r="E49" s="83"/>
+      <c r="D49" s="65"/>
+      <c r="E49" s="82"/>
       <c r="G49" s="52"/>
       <c r="H49" s="52"/>
       <c r="I49" s="51"/>
-      <c r="J49" s="137" t="s">
+      <c r="J49" s="135" t="s">
         <v>66</v>
       </c>
-      <c r="K49" s="138">
+      <c r="K49" s="136">
         <v>6.0</v>
       </c>
-      <c r="L49" s="114"/>
-      <c r="M49" s="115"/>
-      <c r="N49" s="116"/>
-      <c r="O49" s="117"/>
-      <c r="P49" s="118"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="113"/>
+      <c r="N49" s="114"/>
+      <c r="O49" s="115"/>
+      <c r="P49" s="116"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="B50" s="96"/>
+      <c r="B50" s="95"/>
       <c r="C50" s="29"/>
-      <c r="D50" s="75"/>
-      <c r="E50" s="142"/>
+      <c r="D50" s="74"/>
+      <c r="E50" s="140"/>
       <c r="G50" s="52"/>
       <c r="H50" s="52"/>
       <c r="I50" s="51"/>
       <c r="J50" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="K50" s="112">
+      <c r="K50" s="110">
         <v>2.0</v>
       </c>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="B51" s="94"/>
-      <c r="C51" s="65"/>
+      <c r="B51" s="92"/>
+      <c r="C51" s="64"/>
       <c r="D51" s="17"/>
-      <c r="E51" s="83"/>
+      <c r="E51" s="82"/>
       <c r="G51" s="52"/>
       <c r="H51" s="52"/>
       <c r="I51" s="51"/>
       <c r="J51" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="K51" s="138">
+      <c r="K51" s="136">
         <v>4.0</v>
       </c>
-      <c r="L51" s="63"/>
+      <c r="L51" s="38"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="B52" s="100"/>
-      <c r="C52" s="76"/>
+      <c r="B52" s="98"/>
+      <c r="C52" s="75"/>
       <c r="D52" s="29"/>
-      <c r="E52" s="143"/>
+      <c r="E52" s="141"/>
       <c r="G52" s="52"/>
       <c r="H52" s="52"/>
       <c r="I52" s="30"/>
       <c r="J52" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="K52" s="144">
+      <c r="K52" s="142">
         <v>2.0</v>
       </c>
-      <c r="L52" s="140"/>
-      <c r="M52" s="122"/>
-      <c r="N52" s="122"/>
-      <c r="O52" s="122"/>
-      <c r="P52" s="122"/>
-      <c r="Q52" s="122"/>
+      <c r="L52" s="138"/>
+      <c r="M52" s="120"/>
+      <c r="N52" s="120"/>
+      <c r="O52" s="120"/>
+      <c r="P52" s="120"/>
+      <c r="Q52" s="120"/>
     </row>
     <row r="53" ht="18.0" customHeight="1">
-      <c r="B53" s="145" t="s">
+      <c r="B53" s="143" t="s">
         <v>71</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="G53" s="52"/>
       <c r="H53" s="52"/>
-      <c r="I53" s="146" t="s">
+      <c r="I53" s="144" t="s">
         <v>72</v>
       </c>
-      <c r="J53" s="87" t="s">
+      <c r="J53" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="K53" s="147"/>
+      <c r="K53" s="145"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="B54" s="73"/>
-      <c r="C54" s="148"/>
-      <c r="D54" s="148"/>
-      <c r="E54" s="73"/>
+      <c r="B54" s="72"/>
+      <c r="C54" s="146"/>
+      <c r="D54" s="146"/>
+      <c r="E54" s="72"/>
       <c r="G54" s="52"/>
       <c r="H54" s="52"/>
       <c r="I54" s="51"/>
       <c r="J54" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="K54" s="112">
+      <c r="K54" s="110">
         <v>2.0</v>
       </c>
       <c r="L54" s="32"/>
       <c r="M54" s="1"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="E55" s="73"/>
+      <c r="E55" s="72"/>
       <c r="G55" s="52"/>
       <c r="H55" s="52"/>
       <c r="I55" s="51"/>
-      <c r="J55" s="149" t="s">
+      <c r="J55" s="147" t="s">
         <v>74</v>
       </c>
-      <c r="K55" s="138">
+      <c r="K55" s="136">
         <v>1.0</v>
       </c>
       <c r="L55" s="32"/>
       <c r="M55" s="1"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="E56" s="73"/>
+      <c r="E56" s="72"/>
       <c r="G56" s="52"/>
       <c r="H56" s="52"/>
       <c r="I56" s="51"/>
-      <c r="J56" s="137" t="s">
+      <c r="J56" s="135" t="s">
         <v>75</v>
       </c>
-      <c r="K56" s="112"/>
+      <c r="K56" s="110"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
       <c r="O56" s="1"/>
       <c r="Q56" s="1"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="B57" s="150" t="s">
+      <c r="B57" s="148" t="s">
         <v>76</v>
       </c>
-      <c r="C57" s="151" t="s">
+      <c r="C57" s="149" t="s">
         <v>77</v>
       </c>
-      <c r="D57" s="152" t="s">
+      <c r="D57" s="150" t="s">
         <v>78</v>
       </c>
-      <c r="E57" s="73"/>
+      <c r="E57" s="72"/>
       <c r="G57" s="52"/>
       <c r="H57" s="52"/>
       <c r="I57" s="51"/>
       <c r="J57" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="K57" s="138">
+      <c r="K57" s="136">
         <v>1.0</v>
       </c>
       <c r="L57" s="32"/>
       <c r="M57" s="1"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="B58" s="153"/>
-      <c r="C58" s="53"/>
-      <c r="D58" s="54"/>
-      <c r="E58" s="73"/>
+      <c r="B58" s="151"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="55"/>
+      <c r="E58" s="72"/>
       <c r="G58" s="52"/>
       <c r="H58" s="52"/>
       <c r="I58" s="51"/>
-      <c r="J58" s="154" t="s">
+      <c r="J58" s="152" t="s">
         <v>74</v>
       </c>
-      <c r="K58" s="138">
+      <c r="K58" s="136">
         <v>1.0</v>
       </c>
       <c r="L58" s="32"/>
@@ -3903,149 +3897,149 @@
       <c r="Q58" s="1"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="B59" s="155"/>
-      <c r="C59" s="156"/>
+      <c r="B59" s="153"/>
+      <c r="C59" s="154"/>
       <c r="D59" s="50"/>
-      <c r="E59" s="73"/>
-      <c r="F59" s="73"/>
+      <c r="E59" s="72"/>
+      <c r="F59" s="72"/>
       <c r="G59" s="52"/>
       <c r="H59" s="52"/>
       <c r="I59" s="51"/>
-      <c r="J59" s="157" t="s">
+      <c r="J59" s="155" t="s">
         <v>79</v>
       </c>
-      <c r="K59" s="112"/>
+      <c r="K59" s="110"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="B60" s="158"/>
-      <c r="C60" s="156"/>
+      <c r="B60" s="156"/>
+      <c r="C60" s="154"/>
       <c r="D60" s="50"/>
-      <c r="E60" s="73"/>
-      <c r="F60" s="73"/>
+      <c r="E60" s="72"/>
+      <c r="F60" s="72"/>
       <c r="G60" s="52"/>
       <c r="H60" s="52"/>
       <c r="I60" s="51"/>
       <c r="J60" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="K60" s="138">
+      <c r="K60" s="136">
         <v>2.0</v>
       </c>
       <c r="L60" s="32"/>
       <c r="M60" s="1"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="B61" s="155"/>
-      <c r="C61" s="159"/>
-      <c r="D61" s="160"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
+      <c r="B61" s="153"/>
+      <c r="C61" s="157"/>
+      <c r="D61" s="158"/>
+      <c r="E61" s="72"/>
+      <c r="F61" s="72"/>
       <c r="G61" s="52"/>
       <c r="H61" s="52"/>
       <c r="I61" s="51"/>
-      <c r="J61" s="149" t="s">
+      <c r="J61" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="K61" s="138">
+      <c r="K61" s="136">
         <v>1.0</v>
       </c>
       <c r="L61" s="32"/>
       <c r="M61" s="1"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="B62" s="158"/>
-      <c r="C62" s="161"/>
-      <c r="D62" s="162"/>
-      <c r="E62" s="73"/>
-      <c r="F62" s="73"/>
+      <c r="B62" s="156"/>
+      <c r="C62" s="159"/>
+      <c r="D62" s="160"/>
+      <c r="E62" s="72"/>
+      <c r="F62" s="72"/>
       <c r="G62" s="52"/>
       <c r="H62" s="61"/>
       <c r="I62" s="30"/>
-      <c r="J62" s="149" t="s">
+      <c r="J62" s="147" t="s">
         <v>74</v>
       </c>
-      <c r="K62" s="121">
+      <c r="K62" s="119">
         <v>2.0</v>
       </c>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="B63" s="153"/>
-      <c r="C63" s="70"/>
+      <c r="B63" s="151"/>
+      <c r="C63" s="69"/>
       <c r="D63" s="18"/>
-      <c r="E63" s="73"/>
-      <c r="F63" s="73"/>
+      <c r="E63" s="72"/>
+      <c r="F63" s="72"/>
       <c r="G63" s="52"/>
-      <c r="H63" s="163" t="s">
+      <c r="H63" s="161" t="s">
         <v>81</v>
       </c>
-      <c r="I63" s="164" t="s">
+      <c r="I63" s="162" t="s">
         <v>82</v>
       </c>
       <c r="J63" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="K63" s="112">
+      <c r="K63" s="110">
         <v>1.0</v>
       </c>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="B64" s="158"/>
-      <c r="C64" s="161"/>
-      <c r="D64" s="75"/>
-      <c r="E64" s="73"/>
-      <c r="F64" s="73"/>
+      <c r="B64" s="156"/>
+      <c r="C64" s="159"/>
+      <c r="D64" s="74"/>
+      <c r="E64" s="72"/>
+      <c r="F64" s="72"/>
       <c r="G64" s="52"/>
       <c r="H64" s="52"/>
       <c r="I64" s="51"/>
       <c r="J64" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="K64" s="112">
+      <c r="K64" s="110">
         <v>5.0</v>
       </c>
-      <c r="L64" s="114"/>
-      <c r="M64" s="115"/>
-      <c r="N64" s="116"/>
-      <c r="O64" s="117"/>
-      <c r="P64" s="118"/>
+      <c r="L64" s="112"/>
+      <c r="M64" s="113"/>
+      <c r="N64" s="114"/>
+      <c r="O64" s="115"/>
+      <c r="P64" s="116"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="B65" s="155"/>
-      <c r="C65" s="159"/>
-      <c r="D65" s="75"/>
-      <c r="E65" s="73"/>
-      <c r="F65" s="73"/>
+      <c r="B65" s="153"/>
+      <c r="C65" s="157"/>
+      <c r="D65" s="74"/>
+      <c r="E65" s="72"/>
+      <c r="F65" s="72"/>
       <c r="G65" s="52"/>
       <c r="H65" s="52"/>
       <c r="I65" s="51"/>
       <c r="J65" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="K65" s="112">
+      <c r="K65" s="110">
         <v>2.0</v>
       </c>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="B66" s="158"/>
-      <c r="C66" s="161"/>
-      <c r="D66" s="165"/>
-      <c r="E66" s="73"/>
-      <c r="F66" s="73"/>
+      <c r="B66" s="156"/>
+      <c r="C66" s="159"/>
+      <c r="D66" s="163"/>
+      <c r="E66" s="72"/>
+      <c r="F66" s="72"/>
       <c r="G66" s="52"/>
       <c r="H66" s="52"/>
       <c r="I66" s="51"/>
       <c r="J66" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="K66" s="138">
+      <c r="K66" s="136">
         <v>4.0</v>
       </c>
       <c r="L66" s="32"/>
@@ -4060,102 +4054,102 @@
       <c r="U66" s="1"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="B67" s="155"/>
-      <c r="C67" s="159"/>
-      <c r="D67" s="166"/>
-      <c r="E67" s="73"/>
-      <c r="F67" s="73"/>
+      <c r="B67" s="153"/>
+      <c r="C67" s="157"/>
+      <c r="D67" s="164"/>
+      <c r="E67" s="72"/>
+      <c r="F67" s="72"/>
       <c r="G67" s="61"/>
       <c r="H67" s="61"/>
       <c r="I67" s="30"/>
       <c r="J67" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="K67" s="144">
+      <c r="K67" s="142">
         <v>1.0</v>
       </c>
-      <c r="L67" s="140"/>
-      <c r="M67" s="122"/>
-      <c r="N67" s="122"/>
-      <c r="O67" s="122"/>
-      <c r="P67" s="122"/>
-      <c r="Q67" s="122"/>
-      <c r="R67" s="122"/>
-      <c r="S67" s="122"/>
-      <c r="T67" s="122"/>
-      <c r="U67" s="122"/>
-      <c r="V67" s="122"/>
-      <c r="W67" s="122"/>
-      <c r="X67" s="122"/>
-      <c r="Y67" s="122"/>
-      <c r="Z67" s="122"/>
-      <c r="AA67" s="122"/>
-      <c r="AB67" s="122"/>
+      <c r="L67" s="138"/>
+      <c r="M67" s="120"/>
+      <c r="N67" s="120"/>
+      <c r="O67" s="120"/>
+      <c r="P67" s="120"/>
+      <c r="Q67" s="120"/>
+      <c r="R67" s="120"/>
+      <c r="S67" s="120"/>
+      <c r="T67" s="120"/>
+      <c r="U67" s="120"/>
+      <c r="V67" s="120"/>
+      <c r="W67" s="120"/>
+      <c r="X67" s="120"/>
+      <c r="Y67" s="120"/>
+      <c r="Z67" s="120"/>
+      <c r="AA67" s="120"/>
+      <c r="AB67" s="120"/>
     </row>
     <row r="68" ht="24.75" customHeight="1">
-      <c r="B68" s="153"/>
+      <c r="B68" s="151"/>
       <c r="C68" s="59"/>
-      <c r="D68" s="72"/>
-      <c r="E68" s="73"/>
-      <c r="F68" s="73"/>
-      <c r="G68" s="167" t="s">
+      <c r="D68" s="71"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="72"/>
+      <c r="G68" s="165" t="s">
         <v>84</v>
       </c>
-      <c r="H68" s="168" t="s">
+      <c r="H68" s="166" t="s">
         <v>85</v>
       </c>
-      <c r="I68" s="169"/>
-      <c r="J68" s="170" t="s">
+      <c r="I68" s="167"/>
+      <c r="J68" s="168" t="s">
         <v>86</v>
       </c>
-      <c r="K68" s="170">
+      <c r="K68" s="168">
         <v>2.0</v>
       </c>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
     </row>
     <row r="69" ht="24.75" customHeight="1">
-      <c r="B69" s="155"/>
-      <c r="C69" s="159"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="73"/>
+      <c r="B69" s="153"/>
+      <c r="C69" s="157"/>
+      <c r="D69" s="71"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="72"/>
       <c r="G69" s="30"/>
       <c r="H69" s="61"/>
       <c r="I69" s="36"/>
-      <c r="J69" s="171" t="s">
+      <c r="J69" s="169" t="s">
         <v>87</v>
       </c>
-      <c r="K69" s="171">
+      <c r="K69" s="169">
         <v>2.0</v>
       </c>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
     </row>
     <row r="70">
-      <c r="B70" s="158"/>
-      <c r="C70" s="161"/>
-      <c r="D70" s="92"/>
-      <c r="E70" s="73"/>
-      <c r="F70" s="73"/>
-      <c r="G70" s="46" t="s">
+      <c r="B70" s="156"/>
+      <c r="C70" s="159"/>
+      <c r="D70" s="90"/>
+      <c r="E70" s="72"/>
+      <c r="F70" s="72"/>
+      <c r="G70" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="H70" s="172" t="s">
+      <c r="H70" s="170" t="s">
         <v>89</v>
       </c>
       <c r="I70" s="22"/>
-      <c r="J70" s="173" t="s">
+      <c r="J70" s="171" t="s">
         <v>90</v>
       </c>
       <c r="K70" s="22"/>
     </row>
     <row r="71" ht="20.25" customHeight="1">
-      <c r="B71" s="155"/>
-      <c r="C71" s="159"/>
-      <c r="D71" s="92"/>
-      <c r="E71" s="73"/>
-      <c r="F71" s="73"/>
+      <c r="B71" s="153"/>
+      <c r="C71" s="157"/>
+      <c r="D71" s="90"/>
+      <c r="E71" s="72"/>
+      <c r="F71" s="72"/>
       <c r="G71" s="52"/>
       <c r="H71" s="52"/>
       <c r="I71" s="22"/>
@@ -4163,83 +4157,83 @@
       <c r="K71" s="22"/>
     </row>
     <row r="72" ht="28.5" customHeight="1">
-      <c r="B72" s="158"/>
-      <c r="C72" s="161"/>
-      <c r="D72" s="166"/>
-      <c r="E72" s="73"/>
-      <c r="F72" s="73"/>
+      <c r="B72" s="156"/>
+      <c r="C72" s="159"/>
+      <c r="D72" s="164"/>
+      <c r="E72" s="72"/>
+      <c r="F72" s="72"/>
       <c r="G72" s="52"/>
       <c r="H72" s="52"/>
       <c r="I72" s="22"/>
       <c r="J72" s="61"/>
       <c r="K72" s="36"/>
-      <c r="L72" s="122"/>
-      <c r="M72" s="122"/>
-      <c r="N72" s="122"/>
-      <c r="O72" s="122"/>
-      <c r="P72" s="122"/>
-      <c r="Q72" s="122"/>
-      <c r="R72" s="122"/>
-      <c r="S72" s="122"/>
-      <c r="T72" s="122"/>
-      <c r="U72" s="122"/>
-      <c r="V72" s="122"/>
-      <c r="W72" s="122"/>
-      <c r="X72" s="122"/>
-      <c r="Y72" s="122"/>
-      <c r="Z72" s="122"/>
-      <c r="AA72" s="122"/>
-      <c r="AB72" s="122"/>
+      <c r="L72" s="120"/>
+      <c r="M72" s="120"/>
+      <c r="N72" s="120"/>
+      <c r="O72" s="120"/>
+      <c r="P72" s="120"/>
+      <c r="Q72" s="120"/>
+      <c r="R72" s="120"/>
+      <c r="S72" s="120"/>
+      <c r="T72" s="120"/>
+      <c r="U72" s="120"/>
+      <c r="V72" s="120"/>
+      <c r="W72" s="120"/>
+      <c r="X72" s="120"/>
+      <c r="Y72" s="120"/>
+      <c r="Z72" s="120"/>
+      <c r="AA72" s="120"/>
+      <c r="AB72" s="120"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="B73" s="153"/>
+      <c r="B73" s="151"/>
       <c r="C73" s="28"/>
-      <c r="D73" s="82"/>
-      <c r="E73" s="73"/>
-      <c r="F73" s="73"/>
+      <c r="D73" s="81"/>
+      <c r="E73" s="72"/>
+      <c r="F73" s="72"/>
       <c r="G73" s="52"/>
       <c r="H73" s="52"/>
       <c r="I73" s="22"/>
-      <c r="J73" s="127" t="s">
+      <c r="J73" s="125" t="s">
         <v>91</v>
       </c>
-      <c r="K73" s="112">
+      <c r="K73" s="110">
         <v>2.0</v>
       </c>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="B74" s="158"/>
-      <c r="C74" s="161"/>
-      <c r="D74" s="66"/>
-      <c r="E74" s="73"/>
-      <c r="F74" s="73"/>
+      <c r="B74" s="156"/>
+      <c r="C74" s="159"/>
+      <c r="D74" s="65"/>
+      <c r="E74" s="72"/>
+      <c r="F74" s="72"/>
       <c r="G74" s="52"/>
       <c r="H74" s="52"/>
       <c r="I74" s="22"/>
       <c r="J74" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="K74" s="112">
+      <c r="K74" s="110">
         <v>2.0</v>
       </c>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="B75" s="155"/>
-      <c r="C75" s="159"/>
-      <c r="D75" s="66"/>
-      <c r="E75" s="73"/>
-      <c r="F75" s="73"/>
+      <c r="B75" s="153"/>
+      <c r="C75" s="157"/>
+      <c r="D75" s="65"/>
+      <c r="E75" s="72"/>
+      <c r="F75" s="72"/>
       <c r="G75" s="52"/>
       <c r="H75" s="52"/>
       <c r="I75" s="22"/>
       <c r="J75" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="K75" s="112">
+      <c r="K75" s="110">
         <v>2.0</v>
       </c>
       <c r="L75" s="1"/>
@@ -4247,227 +4241,227 @@
       <c r="N75" s="1"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="B76" s="158"/>
-      <c r="C76" s="161"/>
-      <c r="D76" s="174"/>
-      <c r="E76" s="73"/>
-      <c r="F76" s="73"/>
+      <c r="B76" s="156"/>
+      <c r="C76" s="159"/>
+      <c r="D76" s="172"/>
+      <c r="E76" s="72"/>
+      <c r="F76" s="72"/>
       <c r="G76" s="52"/>
       <c r="H76" s="61"/>
       <c r="I76" s="36"/>
-      <c r="J76" s="149" t="s">
+      <c r="J76" s="147" t="s">
         <v>92</v>
       </c>
-      <c r="K76" s="121">
+      <c r="K76" s="119">
         <v>2.0</v>
       </c>
-      <c r="L76" s="122"/>
-      <c r="M76" s="122"/>
-      <c r="N76" s="123"/>
-      <c r="O76" s="122"/>
-      <c r="P76" s="122"/>
-      <c r="Q76" s="122"/>
-      <c r="R76" s="122"/>
+      <c r="L76" s="120"/>
+      <c r="M76" s="120"/>
+      <c r="N76" s="121"/>
+      <c r="O76" s="120"/>
+      <c r="P76" s="120"/>
+      <c r="Q76" s="120"/>
+      <c r="R76" s="120"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="B77" s="155"/>
-      <c r="C77" s="159"/>
-      <c r="D77" s="175"/>
-      <c r="E77" s="73"/>
-      <c r="F77" s="73"/>
+      <c r="B77" s="153"/>
+      <c r="C77" s="157"/>
+      <c r="D77" s="173"/>
+      <c r="E77" s="72"/>
+      <c r="F77" s="72"/>
       <c r="G77" s="52"/>
-      <c r="H77" s="176" t="s">
+      <c r="H77" s="174" t="s">
         <v>93</v>
       </c>
-      <c r="I77" s="141" t="s">
+      <c r="I77" s="139" t="s">
         <v>94</v>
       </c>
       <c r="J77" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="K77" s="112">
+      <c r="K77" s="110">
         <v>1.0</v>
       </c>
-      <c r="L77" s="136"/>
-      <c r="M77" s="136"/>
-      <c r="N77" s="136"/>
-      <c r="O77" s="136"/>
-      <c r="P77" s="136"/>
-      <c r="Q77" s="136"/>
+      <c r="L77" s="134"/>
+      <c r="M77" s="134"/>
+      <c r="N77" s="134"/>
+      <c r="O77" s="134"/>
+      <c r="P77" s="134"/>
+      <c r="Q77" s="134"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="B78" s="153"/>
-      <c r="C78" s="89"/>
-      <c r="D78" s="45"/>
-      <c r="E78" s="73"/>
-      <c r="F78" s="73"/>
+      <c r="B78" s="151"/>
+      <c r="C78" s="87"/>
+      <c r="D78" s="44"/>
+      <c r="E78" s="72"/>
+      <c r="F78" s="72"/>
       <c r="G78" s="52"/>
       <c r="H78" s="52"/>
       <c r="I78" s="51"/>
-      <c r="J78" s="137" t="s">
+      <c r="J78" s="135" t="s">
         <v>66</v>
       </c>
-      <c r="K78" s="138">
+      <c r="K78" s="136">
         <v>6.0</v>
       </c>
-      <c r="L78" s="114"/>
-      <c r="M78" s="115"/>
-      <c r="N78" s="116"/>
-      <c r="O78" s="117"/>
-      <c r="P78" s="118"/>
+      <c r="L78" s="112"/>
+      <c r="M78" s="113"/>
+      <c r="N78" s="114"/>
+      <c r="O78" s="115"/>
+      <c r="P78" s="116"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="B79" s="155"/>
-      <c r="C79" s="159"/>
-      <c r="D79" s="45"/>
-      <c r="E79" s="73"/>
-      <c r="F79" s="73"/>
+      <c r="B79" s="153"/>
+      <c r="C79" s="157"/>
+      <c r="D79" s="44"/>
+      <c r="E79" s="72"/>
+      <c r="F79" s="72"/>
       <c r="G79" s="52"/>
       <c r="H79" s="52"/>
       <c r="I79" s="51"/>
       <c r="J79" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="K79" s="112">
+      <c r="K79" s="110">
         <v>2.0</v>
       </c>
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="B80" s="158"/>
-      <c r="C80" s="161"/>
-      <c r="D80" s="77"/>
-      <c r="E80" s="73"/>
-      <c r="F80" s="73"/>
+      <c r="B80" s="156"/>
+      <c r="C80" s="159"/>
+      <c r="D80" s="76"/>
+      <c r="E80" s="72"/>
+      <c r="F80" s="72"/>
       <c r="G80" s="52"/>
       <c r="H80" s="52"/>
       <c r="I80" s="51"/>
       <c r="J80" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="K80" s="138">
+      <c r="K80" s="136">
         <v>3.0</v>
       </c>
       <c r="L80" s="2"/>
-      <c r="M80" s="177"/>
+      <c r="M80" s="175"/>
       <c r="N80" s="1"/>
       <c r="O80" s="1"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="B81" s="155"/>
-      <c r="C81" s="159"/>
-      <c r="D81" s="77"/>
-      <c r="E81" s="73"/>
-      <c r="F81" s="73"/>
+      <c r="B81" s="153"/>
+      <c r="C81" s="157"/>
+      <c r="D81" s="76"/>
+      <c r="E81" s="72"/>
+      <c r="F81" s="72"/>
       <c r="G81" s="52"/>
       <c r="H81" s="52"/>
       <c r="I81" s="30"/>
       <c r="J81" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="K81" s="144">
+      <c r="K81" s="142">
         <v>2.0</v>
       </c>
-      <c r="L81" s="178"/>
-      <c r="M81" s="122"/>
-      <c r="N81" s="123"/>
-      <c r="O81" s="122"/>
-      <c r="P81" s="122"/>
-      <c r="Q81" s="122"/>
-      <c r="R81" s="122"/>
-      <c r="S81" s="122"/>
-      <c r="T81" s="122"/>
-      <c r="U81" s="122"/>
-      <c r="V81" s="122"/>
-      <c r="W81" s="122"/>
-      <c r="X81" s="122"/>
-      <c r="Y81" s="122"/>
-      <c r="Z81" s="122"/>
-      <c r="AA81" s="122"/>
-      <c r="AB81" s="122"/>
+      <c r="L81" s="176"/>
+      <c r="M81" s="120"/>
+      <c r="N81" s="121"/>
+      <c r="O81" s="120"/>
+      <c r="P81" s="120"/>
+      <c r="Q81" s="120"/>
+      <c r="R81" s="120"/>
+      <c r="S81" s="120"/>
+      <c r="T81" s="120"/>
+      <c r="U81" s="120"/>
+      <c r="V81" s="120"/>
+      <c r="W81" s="120"/>
+      <c r="X81" s="120"/>
+      <c r="Y81" s="120"/>
+      <c r="Z81" s="120"/>
+      <c r="AA81" s="120"/>
+      <c r="AB81" s="120"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="B82" s="179"/>
-      <c r="C82" s="180"/>
-      <c r="D82" s="181"/>
-      <c r="E82" s="73"/>
-      <c r="F82" s="73"/>
+      <c r="B82" s="177"/>
+      <c r="C82" s="178"/>
+      <c r="D82" s="179"/>
+      <c r="E82" s="72"/>
+      <c r="F82" s="72"/>
       <c r="G82" s="52"/>
       <c r="H82" s="52"/>
-      <c r="I82" s="141" t="s">
+      <c r="I82" s="139" t="s">
         <v>95</v>
       </c>
       <c r="J82" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="K82" s="112">
+      <c r="K82" s="110">
         <v>1.0</v>
       </c>
-      <c r="L82" s="182"/>
-      <c r="M82" s="136"/>
-      <c r="N82" s="136"/>
-      <c r="O82" s="136"/>
-      <c r="P82" s="136"/>
-      <c r="Q82" s="136"/>
+      <c r="L82" s="180"/>
+      <c r="M82" s="134"/>
+      <c r="N82" s="134"/>
+      <c r="O82" s="134"/>
+      <c r="P82" s="134"/>
+      <c r="Q82" s="134"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
-      <c r="E83" s="73"/>
-      <c r="F83" s="73"/>
+      <c r="E83" s="72"/>
+      <c r="F83" s="72"/>
       <c r="G83" s="52"/>
       <c r="H83" s="52"/>
       <c r="I83" s="51"/>
-      <c r="J83" s="137" t="s">
+      <c r="J83" s="135" t="s">
         <v>66</v>
       </c>
-      <c r="K83" s="138">
+      <c r="K83" s="136">
         <v>6.0</v>
       </c>
-      <c r="L83" s="183"/>
-      <c r="M83" s="115"/>
-      <c r="N83" s="116"/>
-      <c r="O83" s="117"/>
-      <c r="P83" s="118"/>
+      <c r="L83" s="181"/>
+      <c r="M83" s="113"/>
+      <c r="N83" s="114"/>
+      <c r="O83" s="115"/>
+      <c r="P83" s="116"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="B84" s="150" t="s">
+      <c r="B84" s="148" t="s">
         <v>96</v>
       </c>
-      <c r="C84" s="151" t="s">
+      <c r="C84" s="149" t="s">
         <v>77</v>
       </c>
-      <c r="D84" s="152" t="s">
+      <c r="D84" s="150" t="s">
         <v>78</v>
       </c>
-      <c r="E84" s="73"/>
-      <c r="F84" s="73"/>
+      <c r="E84" s="72"/>
+      <c r="F84" s="72"/>
       <c r="G84" s="52"/>
       <c r="H84" s="52"/>
       <c r="I84" s="51"/>
       <c r="J84" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="K84" s="112">
+      <c r="K84" s="110">
         <v>2.0</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="1"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="B85" s="153"/>
-      <c r="C85" s="53"/>
-      <c r="D85" s="54"/>
-      <c r="E85" s="73"/>
-      <c r="F85" s="73"/>
+      <c r="B85" s="151"/>
+      <c r="C85" s="54"/>
+      <c r="D85" s="55"/>
+      <c r="E85" s="72"/>
+      <c r="F85" s="72"/>
       <c r="G85" s="52"/>
       <c r="H85" s="52"/>
       <c r="I85" s="51"/>
       <c r="J85" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="K85" s="138">
+      <c r="K85" s="136">
         <v>3.0</v>
       </c>
       <c r="L85" s="2"/>
@@ -4475,26 +4469,26 @@
       <c r="N85" s="1"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="B86" s="155"/>
-      <c r="C86" s="156"/>
+      <c r="B86" s="153"/>
+      <c r="C86" s="154"/>
       <c r="D86" s="50"/>
-      <c r="E86" s="73"/>
-      <c r="F86" s="73"/>
+      <c r="E86" s="72"/>
+      <c r="F86" s="72"/>
       <c r="G86" s="52"/>
       <c r="H86" s="52"/>
       <c r="I86" s="30"/>
-      <c r="J86" s="95" t="s">
+      <c r="J86" s="93" t="s">
         <v>69</v>
       </c>
-      <c r="K86" s="184">
+      <c r="K86" s="182">
         <v>2.0</v>
       </c>
-      <c r="L86" s="178"/>
-      <c r="M86" s="122"/>
-      <c r="N86" s="122"/>
-      <c r="O86" s="122"/>
-      <c r="P86" s="122"/>
-      <c r="Q86" s="122"/>
+      <c r="L86" s="176"/>
+      <c r="M86" s="120"/>
+      <c r="N86" s="120"/>
+      <c r="O86" s="120"/>
+      <c r="P86" s="120"/>
+      <c r="Q86" s="120"/>
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
       <c r="T86" s="1"/>
@@ -4505,294 +4499,294 @@
       <c r="AA86" s="1"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="B87" s="158"/>
-      <c r="C87" s="156"/>
+      <c r="B87" s="156"/>
+      <c r="C87" s="154"/>
       <c r="D87" s="50"/>
-      <c r="E87" s="73"/>
-      <c r="F87" s="73"/>
+      <c r="E87" s="72"/>
+      <c r="F87" s="72"/>
       <c r="G87" s="52"/>
       <c r="H87" s="52"/>
-      <c r="I87" s="185" t="s">
+      <c r="I87" s="183" t="s">
         <v>97</v>
       </c>
-      <c r="J87" s="137" t="s">
+      <c r="J87" s="135" t="s">
         <v>98</v>
       </c>
-      <c r="K87" s="112"/>
-      <c r="L87" s="182"/>
-      <c r="M87" s="136"/>
-      <c r="N87" s="136"/>
-      <c r="O87" s="136"/>
-      <c r="P87" s="136"/>
+      <c r="K87" s="110"/>
+      <c r="L87" s="180"/>
+      <c r="M87" s="134"/>
+      <c r="N87" s="134"/>
+      <c r="O87" s="134"/>
+      <c r="P87" s="134"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="B88" s="155"/>
-      <c r="C88" s="156"/>
-      <c r="D88" s="186"/>
-      <c r="E88" s="73"/>
-      <c r="F88" s="73"/>
+      <c r="B88" s="153"/>
+      <c r="C88" s="154"/>
+      <c r="D88" s="184"/>
+      <c r="E88" s="72"/>
+      <c r="F88" s="72"/>
       <c r="G88" s="52"/>
       <c r="H88" s="52"/>
       <c r="I88" s="51"/>
       <c r="J88" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="K88" s="112">
+      <c r="K88" s="110">
         <v>1.0</v>
       </c>
       <c r="L88" s="2"/>
       <c r="N88" s="1"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="B89" s="158"/>
-      <c r="C89" s="161"/>
-      <c r="D89" s="187"/>
-      <c r="E89" s="73"/>
-      <c r="F89" s="73"/>
+      <c r="B89" s="156"/>
+      <c r="C89" s="159"/>
+      <c r="D89" s="185"/>
+      <c r="E89" s="72"/>
+      <c r="F89" s="72"/>
       <c r="G89" s="52"/>
       <c r="H89" s="52"/>
       <c r="I89" s="51"/>
-      <c r="J89" s="149" t="s">
+      <c r="J89" s="147" t="s">
         <v>68</v>
       </c>
-      <c r="K89" s="144">
+      <c r="K89" s="142">
         <v>1.0</v>
       </c>
-      <c r="L89" s="178"/>
-      <c r="M89" s="122"/>
-      <c r="N89" s="122"/>
-      <c r="O89" s="122"/>
-      <c r="P89" s="122"/>
-      <c r="Q89" s="122"/>
-      <c r="R89" s="122"/>
-      <c r="S89" s="122"/>
-      <c r="T89" s="122"/>
-      <c r="U89" s="122"/>
-      <c r="V89" s="122"/>
-      <c r="W89" s="122"/>
-      <c r="X89" s="122"/>
-      <c r="Y89" s="122"/>
-      <c r="Z89" s="122"/>
-      <c r="AA89" s="122"/>
-      <c r="AB89" s="122"/>
+      <c r="L89" s="176"/>
+      <c r="M89" s="120"/>
+      <c r="N89" s="120"/>
+      <c r="O89" s="120"/>
+      <c r="P89" s="120"/>
+      <c r="Q89" s="120"/>
+      <c r="R89" s="120"/>
+      <c r="S89" s="120"/>
+      <c r="T89" s="120"/>
+      <c r="U89" s="120"/>
+      <c r="V89" s="120"/>
+      <c r="W89" s="120"/>
+      <c r="X89" s="120"/>
+      <c r="Y89" s="120"/>
+      <c r="Z89" s="120"/>
+      <c r="AA89" s="120"/>
+      <c r="AB89" s="120"/>
       <c r="AC89" s="1"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="B90" s="155"/>
-      <c r="C90" s="159"/>
-      <c r="D90" s="175"/>
-      <c r="E90" s="73"/>
-      <c r="F90" s="73"/>
+      <c r="B90" s="153"/>
+      <c r="C90" s="157"/>
+      <c r="D90" s="173"/>
+      <c r="E90" s="72"/>
+      <c r="F90" s="72"/>
       <c r="G90" s="52"/>
       <c r="H90" s="52"/>
       <c r="I90" s="51"/>
-      <c r="J90" s="137" t="s">
+      <c r="J90" s="135" t="s">
         <v>100</v>
       </c>
-      <c r="K90" s="112"/>
+      <c r="K90" s="110"/>
       <c r="L90" s="2"/>
       <c r="M90" s="1"/>
       <c r="N90" s="1"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="B91" s="153"/>
-      <c r="C91" s="70"/>
+      <c r="B91" s="151"/>
+      <c r="C91" s="69"/>
       <c r="D91" s="18"/>
-      <c r="E91" s="73"/>
-      <c r="F91" s="73"/>
+      <c r="E91" s="72"/>
+      <c r="F91" s="72"/>
       <c r="G91" s="52"/>
       <c r="H91" s="52"/>
       <c r="I91" s="51"/>
       <c r="J91" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="K91" s="112">
+      <c r="K91" s="110">
         <v>1.0</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="1"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="B92" s="155"/>
-      <c r="C92" s="159"/>
-      <c r="D92" s="75"/>
-      <c r="E92" s="73"/>
-      <c r="F92" s="73"/>
+      <c r="B92" s="153"/>
+      <c r="C92" s="157"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="72"/>
+      <c r="F92" s="72"/>
       <c r="G92" s="52"/>
       <c r="H92" s="52"/>
       <c r="I92" s="51"/>
-      <c r="J92" s="149" t="s">
+      <c r="J92" s="147" t="s">
         <v>102</v>
       </c>
-      <c r="K92" s="121">
+      <c r="K92" s="119">
         <v>1.0</v>
       </c>
-      <c r="L92" s="178"/>
-      <c r="M92" s="122"/>
-      <c r="N92" s="122"/>
-      <c r="O92" s="122"/>
-      <c r="P92" s="122"/>
-      <c r="Q92" s="122"/>
-      <c r="R92" s="122"/>
-      <c r="S92" s="122"/>
-      <c r="T92" s="122"/>
-      <c r="U92" s="122"/>
-      <c r="V92" s="122"/>
-      <c r="W92" s="122"/>
-      <c r="X92" s="122"/>
-      <c r="Y92" s="122"/>
-      <c r="Z92" s="122"/>
-      <c r="AA92" s="122"/>
-      <c r="AB92" s="122"/>
+      <c r="L92" s="176"/>
+      <c r="M92" s="120"/>
+      <c r="N92" s="120"/>
+      <c r="O92" s="120"/>
+      <c r="P92" s="120"/>
+      <c r="Q92" s="120"/>
+      <c r="R92" s="120"/>
+      <c r="S92" s="120"/>
+      <c r="T92" s="120"/>
+      <c r="U92" s="120"/>
+      <c r="V92" s="120"/>
+      <c r="W92" s="120"/>
+      <c r="X92" s="120"/>
+      <c r="Y92" s="120"/>
+      <c r="Z92" s="120"/>
+      <c r="AA92" s="120"/>
+      <c r="AB92" s="120"/>
       <c r="AC92" s="1"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="B93" s="158"/>
-      <c r="C93" s="161"/>
-      <c r="D93" s="75"/>
-      <c r="E93" s="73"/>
-      <c r="F93" s="73"/>
+      <c r="B93" s="156"/>
+      <c r="C93" s="159"/>
+      <c r="D93" s="74"/>
+      <c r="E93" s="72"/>
+      <c r="F93" s="72"/>
       <c r="G93" s="52"/>
       <c r="H93" s="52"/>
       <c r="I93" s="51"/>
-      <c r="J93" s="137" t="s">
+      <c r="J93" s="135" t="s">
         <v>103</v>
       </c>
-      <c r="K93" s="112"/>
+      <c r="K93" s="110"/>
       <c r="L93" s="2"/>
       <c r="M93" s="1"/>
       <c r="N93" s="1"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="B94" s="155"/>
-      <c r="C94" s="159"/>
-      <c r="D94" s="165"/>
-      <c r="E94" s="73"/>
-      <c r="F94" s="73"/>
+      <c r="B94" s="153"/>
+      <c r="C94" s="157"/>
+      <c r="D94" s="163"/>
+      <c r="E94" s="72"/>
+      <c r="F94" s="72"/>
       <c r="G94" s="52"/>
       <c r="H94" s="52"/>
       <c r="I94" s="51"/>
       <c r="J94" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="K94" s="138">
+      <c r="K94" s="136">
         <v>1.0</v>
       </c>
-      <c r="L94" s="178"/>
-      <c r="M94" s="122"/>
+      <c r="L94" s="176"/>
+      <c r="M94" s="120"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="B95" s="158"/>
-      <c r="C95" s="161"/>
-      <c r="D95" s="174"/>
-      <c r="E95" s="73"/>
-      <c r="F95" s="73"/>
+      <c r="B95" s="156"/>
+      <c r="C95" s="159"/>
+      <c r="D95" s="172"/>
+      <c r="E95" s="72"/>
+      <c r="F95" s="72"/>
       <c r="G95" s="52"/>
       <c r="H95" s="61"/>
       <c r="I95" s="30"/>
-      <c r="J95" s="149" t="s">
+      <c r="J95" s="147" t="s">
         <v>102</v>
       </c>
-      <c r="K95" s="144">
+      <c r="K95" s="142">
         <v>1.0</v>
       </c>
-      <c r="L95" s="178"/>
-      <c r="M95" s="122"/>
-      <c r="N95" s="122"/>
-      <c r="O95" s="122"/>
-      <c r="P95" s="122"/>
-      <c r="Q95" s="122"/>
-      <c r="R95" s="122"/>
-      <c r="S95" s="122"/>
-      <c r="T95" s="122"/>
-      <c r="U95" s="122"/>
-      <c r="V95" s="122"/>
-      <c r="W95" s="122"/>
-      <c r="X95" s="122"/>
-      <c r="Y95" s="122"/>
-      <c r="Z95" s="122"/>
-      <c r="AA95" s="122"/>
-      <c r="AB95" s="122"/>
+      <c r="L95" s="176"/>
+      <c r="M95" s="120"/>
+      <c r="N95" s="120"/>
+      <c r="O95" s="120"/>
+      <c r="P95" s="120"/>
+      <c r="Q95" s="120"/>
+      <c r="R95" s="120"/>
+      <c r="S95" s="120"/>
+      <c r="T95" s="120"/>
+      <c r="U95" s="120"/>
+      <c r="V95" s="120"/>
+      <c r="W95" s="120"/>
+      <c r="X95" s="120"/>
+      <c r="Y95" s="120"/>
+      <c r="Z95" s="120"/>
+      <c r="AA95" s="120"/>
+      <c r="AB95" s="120"/>
       <c r="AC95" s="1"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="B96" s="155"/>
-      <c r="C96" s="159"/>
-      <c r="D96" s="175"/>
-      <c r="E96" s="188"/>
-      <c r="F96" s="188"/>
+      <c r="B96" s="153"/>
+      <c r="C96" s="157"/>
+      <c r="D96" s="173"/>
+      <c r="E96" s="186"/>
+      <c r="F96" s="186"/>
       <c r="G96" s="52"/>
-      <c r="H96" s="176" t="s">
+      <c r="H96" s="174" t="s">
         <v>104</v>
       </c>
-      <c r="I96" s="189" t="s">
+      <c r="I96" s="187" t="s">
         <v>105</v>
       </c>
       <c r="J96" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="K96" s="112">
+      <c r="K96" s="110">
         <v>3.0</v>
       </c>
-      <c r="L96" s="182"/>
-      <c r="M96" s="136"/>
-      <c r="N96" s="136"/>
-      <c r="O96" s="136"/>
-      <c r="P96" s="136"/>
-      <c r="Q96" s="136"/>
+      <c r="L96" s="180"/>
+      <c r="M96" s="134"/>
+      <c r="N96" s="134"/>
+      <c r="O96" s="134"/>
+      <c r="P96" s="134"/>
+      <c r="Q96" s="134"/>
     </row>
     <row r="97">
-      <c r="B97" s="153"/>
+      <c r="B97" s="151"/>
       <c r="C97" s="59"/>
-      <c r="D97" s="72"/>
-      <c r="E97" s="188"/>
-      <c r="F97" s="188"/>
+      <c r="D97" s="71"/>
+      <c r="E97" s="186"/>
+      <c r="F97" s="186"/>
       <c r="G97" s="52"/>
       <c r="H97" s="52"/>
       <c r="I97" s="51"/>
-      <c r="J97" s="137" t="s">
+      <c r="J97" s="135" t="s">
         <v>66</v>
       </c>
-      <c r="K97" s="138">
+      <c r="K97" s="136">
         <v>6.0</v>
       </c>
-      <c r="L97" s="183"/>
-      <c r="M97" s="115"/>
-      <c r="N97" s="116"/>
-      <c r="O97" s="117"/>
-      <c r="P97" s="118"/>
+      <c r="L97" s="181"/>
+      <c r="M97" s="113"/>
+      <c r="N97" s="114"/>
+      <c r="O97" s="115"/>
+      <c r="P97" s="116"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="B98" s="155"/>
-      <c r="C98" s="159"/>
-      <c r="D98" s="72"/>
-      <c r="E98" s="188"/>
-      <c r="F98" s="188"/>
+      <c r="B98" s="153"/>
+      <c r="C98" s="157"/>
+      <c r="D98" s="71"/>
+      <c r="E98" s="186"/>
+      <c r="F98" s="186"/>
       <c r="G98" s="52"/>
       <c r="H98" s="52"/>
       <c r="I98" s="51"/>
       <c r="J98" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="K98" s="112">
+      <c r="K98" s="110">
         <v>2.0</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="1"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="B99" s="158"/>
-      <c r="C99" s="161"/>
-      <c r="D99" s="92"/>
-      <c r="E99" s="188"/>
-      <c r="F99" s="188"/>
+      <c r="B99" s="156"/>
+      <c r="C99" s="159"/>
+      <c r="D99" s="90"/>
+      <c r="E99" s="186"/>
+      <c r="F99" s="186"/>
       <c r="G99" s="52"/>
       <c r="H99" s="52"/>
       <c r="I99" s="51"/>
       <c r="J99" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="K99" s="138">
+      <c r="K99" s="136">
         <v>4.0</v>
       </c>
       <c r="L99" s="2"/>
@@ -4802,131 +4796,131 @@
       <c r="P99" s="1"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="B100" s="155"/>
-      <c r="C100" s="159"/>
-      <c r="D100" s="92"/>
-      <c r="E100" s="73"/>
-      <c r="F100" s="73"/>
+      <c r="B100" s="153"/>
+      <c r="C100" s="157"/>
+      <c r="D100" s="90"/>
+      <c r="E100" s="72"/>
+      <c r="F100" s="72"/>
       <c r="G100" s="61"/>
       <c r="H100" s="61"/>
       <c r="I100" s="30"/>
       <c r="J100" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="K100" s="121">
+      <c r="K100" s="119">
         <v>2.0</v>
       </c>
-      <c r="L100" s="178"/>
-      <c r="M100" s="122"/>
-      <c r="N100" s="122"/>
-      <c r="O100" s="122"/>
-      <c r="P100" s="122"/>
-      <c r="Q100" s="122"/>
-      <c r="R100" s="122"/>
-      <c r="S100" s="122"/>
-      <c r="T100" s="122"/>
-      <c r="U100" s="122"/>
-      <c r="V100" s="122"/>
-      <c r="W100" s="122"/>
-      <c r="X100" s="122"/>
-      <c r="Y100" s="122"/>
-      <c r="Z100" s="122"/>
-      <c r="AA100" s="122"/>
-      <c r="AB100" s="122"/>
+      <c r="L100" s="176"/>
+      <c r="M100" s="120"/>
+      <c r="N100" s="120"/>
+      <c r="O100" s="120"/>
+      <c r="P100" s="120"/>
+      <c r="Q100" s="120"/>
+      <c r="R100" s="120"/>
+      <c r="S100" s="120"/>
+      <c r="T100" s="120"/>
+      <c r="U100" s="120"/>
+      <c r="V100" s="120"/>
+      <c r="W100" s="120"/>
+      <c r="X100" s="120"/>
+      <c r="Y100" s="120"/>
+      <c r="Z100" s="120"/>
+      <c r="AA100" s="120"/>
+      <c r="AB100" s="120"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="B101" s="158"/>
-      <c r="C101" s="161"/>
-      <c r="D101" s="92"/>
-      <c r="E101" s="73"/>
-      <c r="F101" s="73"/>
-      <c r="G101" s="46" t="s">
+      <c r="B101" s="156"/>
+      <c r="C101" s="159"/>
+      <c r="D101" s="90"/>
+      <c r="E101" s="72"/>
+      <c r="F101" s="72"/>
+      <c r="G101" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="H101" s="190" t="s">
+      <c r="H101" s="188" t="s">
         <v>107</v>
       </c>
       <c r="I101" s="22"/>
       <c r="J101" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="K101" s="112">
+      <c r="K101" s="110">
         <v>2.0</v>
       </c>
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
-      <c r="N101" s="136"/>
-      <c r="O101" s="136"/>
-      <c r="P101" s="136"/>
-      <c r="Q101" s="136"/>
+      <c r="N101" s="134"/>
+      <c r="O101" s="134"/>
+      <c r="P101" s="134"/>
+      <c r="Q101" s="134"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="B102" s="155"/>
-      <c r="C102" s="159"/>
-      <c r="D102" s="166"/>
-      <c r="E102" s="73"/>
-      <c r="F102" s="73"/>
+      <c r="B102" s="153"/>
+      <c r="C102" s="157"/>
+      <c r="D102" s="164"/>
+      <c r="E102" s="72"/>
+      <c r="F102" s="72"/>
       <c r="G102" s="61"/>
       <c r="H102" s="61"/>
       <c r="I102" s="36"/>
       <c r="J102" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="K102" s="121">
+      <c r="K102" s="119">
         <v>2.0</v>
       </c>
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
-      <c r="N102" s="122"/>
-      <c r="O102" s="122"/>
-      <c r="P102" s="122"/>
-      <c r="Q102" s="122"/>
-      <c r="R102" s="122"/>
-      <c r="S102" s="122"/>
-      <c r="T102" s="122"/>
-      <c r="U102" s="122"/>
-      <c r="V102" s="122"/>
-      <c r="W102" s="122"/>
-      <c r="X102" s="122"/>
-      <c r="Y102" s="122"/>
-      <c r="Z102" s="122"/>
-      <c r="AA102" s="122"/>
-      <c r="AB102" s="122"/>
+      <c r="N102" s="120"/>
+      <c r="O102" s="120"/>
+      <c r="P102" s="120"/>
+      <c r="Q102" s="120"/>
+      <c r="R102" s="120"/>
+      <c r="S102" s="120"/>
+      <c r="T102" s="120"/>
+      <c r="U102" s="120"/>
+      <c r="V102" s="120"/>
+      <c r="W102" s="120"/>
+      <c r="X102" s="120"/>
+      <c r="Y102" s="120"/>
+      <c r="Z102" s="120"/>
+      <c r="AA102" s="120"/>
+      <c r="AB102" s="120"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="B103" s="153"/>
+      <c r="B103" s="151"/>
       <c r="C103" s="28"/>
-      <c r="D103" s="82"/>
-      <c r="E103" s="73"/>
-      <c r="F103" s="73"/>
-      <c r="G103" s="46" t="s">
+      <c r="D103" s="81"/>
+      <c r="E103" s="72"/>
+      <c r="F103" s="72"/>
+      <c r="G103" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="H103" s="46" t="s">
+      <c r="H103" s="45" t="s">
         <v>111</v>
       </c>
       <c r="I103" s="22"/>
       <c r="J103" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="K103" s="191" t="s">
+      <c r="K103" s="189" t="s">
         <v>113</v>
       </c>
-      <c r="L103" s="136" t="s">
+      <c r="L103" s="134" t="s">
         <v>114</v>
       </c>
-      <c r="M103" s="136"/>
-      <c r="N103" s="136"/>
-      <c r="O103" s="136"/>
-      <c r="P103" s="136"/>
-      <c r="Q103" s="136"/>
+      <c r="M103" s="134"/>
+      <c r="N103" s="134"/>
+      <c r="O103" s="134"/>
+      <c r="P103" s="134"/>
+      <c r="Q103" s="134"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="B104" s="155"/>
-      <c r="C104" s="159"/>
-      <c r="D104" s="66"/>
-      <c r="E104" s="73"/>
-      <c r="F104" s="73"/>
+      <c r="B104" s="153"/>
+      <c r="C104" s="157"/>
+      <c r="D104" s="65"/>
+      <c r="E104" s="72"/>
+      <c r="F104" s="72"/>
       <c r="G104" s="61"/>
       <c r="H104" s="61"/>
       <c r="I104" s="36"/>
@@ -4937,136 +4931,136 @@
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="B105" s="158"/>
-      <c r="C105" s="161"/>
-      <c r="D105" s="66"/>
-      <c r="E105" s="73"/>
-      <c r="F105" s="73"/>
+      <c r="B105" s="156"/>
+      <c r="C105" s="159"/>
+      <c r="D105" s="65"/>
+      <c r="E105" s="72"/>
+      <c r="F105" s="72"/>
       <c r="G105" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="H105" s="192" t="s">
+      <c r="H105" s="190" t="s">
         <v>117</v>
       </c>
-      <c r="I105" s="169"/>
-      <c r="J105" s="47" t="s">
+      <c r="I105" s="167"/>
+      <c r="J105" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="K105" s="193">
+      <c r="K105" s="191">
         <v>4.0</v>
       </c>
-      <c r="L105" s="194"/>
-      <c r="M105" s="195"/>
-      <c r="N105" s="196"/>
-      <c r="O105" s="196"/>
-      <c r="P105" s="197"/>
-      <c r="Q105" s="197"/>
-      <c r="R105" s="197"/>
-      <c r="S105" s="198"/>
-      <c r="T105" s="198"/>
-      <c r="U105" s="198"/>
-      <c r="V105" s="198"/>
-      <c r="W105" s="198"/>
-      <c r="X105" s="198"/>
-      <c r="Y105" s="198"/>
-      <c r="Z105" s="198"/>
-      <c r="AA105" s="198"/>
-      <c r="AB105" s="198"/>
+      <c r="L105" s="192"/>
+      <c r="M105" s="193"/>
+      <c r="N105" s="194"/>
+      <c r="O105" s="194"/>
+      <c r="P105" s="195"/>
+      <c r="Q105" s="195"/>
+      <c r="R105" s="195"/>
+      <c r="S105" s="196"/>
+      <c r="T105" s="196"/>
+      <c r="U105" s="196"/>
+      <c r="V105" s="196"/>
+      <c r="W105" s="196"/>
+      <c r="X105" s="196"/>
+      <c r="Y105" s="196"/>
+      <c r="Z105" s="196"/>
+      <c r="AA105" s="196"/>
+      <c r="AB105" s="196"/>
       <c r="AC105" s="21"/>
       <c r="AD105" s="21"/>
       <c r="AE105" s="21"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="B106" s="155"/>
-      <c r="C106" s="159"/>
-      <c r="D106" s="66"/>
-      <c r="E106" s="73"/>
-      <c r="F106" s="73"/>
+      <c r="B106" s="153"/>
+      <c r="C106" s="157"/>
+      <c r="D106" s="65"/>
+      <c r="E106" s="72"/>
+      <c r="F106" s="72"/>
       <c r="G106" s="30"/>
       <c r="H106" s="61"/>
       <c r="I106" s="36"/>
       <c r="J106" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="K106" s="199">
+      <c r="K106" s="197">
         <v>3.0</v>
       </c>
-      <c r="L106" s="200"/>
-      <c r="M106" s="201"/>
-      <c r="N106" s="201"/>
-      <c r="O106" s="202"/>
-      <c r="P106" s="202"/>
-      <c r="Q106" s="202"/>
-      <c r="R106" s="202"/>
-      <c r="S106" s="122"/>
+      <c r="L106" s="198"/>
+      <c r="M106" s="199"/>
+      <c r="N106" s="199"/>
+      <c r="O106" s="200"/>
+      <c r="P106" s="200"/>
+      <c r="Q106" s="200"/>
+      <c r="R106" s="200"/>
+      <c r="S106" s="120"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="B107" s="158"/>
-      <c r="C107" s="161"/>
-      <c r="D107" s="66"/>
-      <c r="E107" s="73"/>
-      <c r="F107" s="73"/>
-      <c r="G107" s="203">
+      <c r="B107" s="156"/>
+      <c r="C107" s="159"/>
+      <c r="D107" s="65"/>
+      <c r="E107" s="72"/>
+      <c r="F107" s="72"/>
+      <c r="G107" s="201">
         <v>0.7708333333333334</v>
       </c>
-      <c r="H107" s="204" t="s">
+      <c r="H107" s="202" t="s">
         <v>119</v>
       </c>
-      <c r="I107" s="169"/>
+      <c r="I107" s="167"/>
       <c r="J107" s="3"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="B108" s="155"/>
-      <c r="C108" s="159"/>
-      <c r="D108" s="175"/>
-      <c r="E108" s="73"/>
-      <c r="F108" s="73"/>
+      <c r="B108" s="153"/>
+      <c r="C108" s="157"/>
+      <c r="D108" s="173"/>
+      <c r="E108" s="72"/>
+      <c r="F108" s="72"/>
       <c r="G108" s="30"/>
       <c r="H108" s="61"/>
       <c r="I108" s="36"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="B109" s="153"/>
-      <c r="C109" s="89"/>
-      <c r="D109" s="45"/>
-      <c r="E109" s="73"/>
-      <c r="F109" s="73"/>
+      <c r="B109" s="151"/>
+      <c r="C109" s="87"/>
+      <c r="D109" s="44"/>
+      <c r="E109" s="72"/>
+      <c r="F109" s="72"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="B110" s="155"/>
-      <c r="C110" s="159"/>
-      <c r="D110" s="77"/>
-      <c r="E110" s="73"/>
-      <c r="F110" s="73"/>
-      <c r="G110" s="205" t="s">
+      <c r="B110" s="153"/>
+      <c r="C110" s="157"/>
+      <c r="D110" s="76"/>
+      <c r="E110" s="72"/>
+      <c r="F110" s="72"/>
+      <c r="G110" s="203" t="s">
         <v>120</v>
       </c>
-      <c r="H110" s="80" t="s">
+      <c r="H110" s="79" t="s">
         <v>121</v>
       </c>
       <c r="I110" s="14"/>
       <c r="J110" s="10"/>
-      <c r="K110" s="206">
+      <c r="K110" s="204">
         <v>1.0</v>
       </c>
-      <c r="L110" s="206"/>
+      <c r="L110" s="204"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="B111" s="158"/>
-      <c r="C111" s="161"/>
-      <c r="D111" s="77"/>
-      <c r="E111" s="73"/>
-      <c r="F111" s="73"/>
+      <c r="B111" s="156"/>
+      <c r="C111" s="159"/>
+      <c r="D111" s="76"/>
+      <c r="E111" s="72"/>
+      <c r="F111" s="72"/>
       <c r="H111" s="3"/>
       <c r="I111" s="3"/>
       <c r="J111" s="3"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="B112" s="207"/>
-      <c r="C112" s="208"/>
-      <c r="D112" s="181"/>
-      <c r="E112" s="73"/>
-      <c r="F112" s="73"/>
+      <c r="B112" s="205"/>
+      <c r="C112" s="206"/>
+      <c r="D112" s="179"/>
+      <c r="E112" s="72"/>
+      <c r="F112" s="72"/>
       <c r="H112" s="3"/>
       <c r="I112" s="3"/>
       <c r="J112" s="3"/>
@@ -5074,38 +5068,38 @@
     <row r="113" ht="15.75" customHeight="1">
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
-      <c r="E113" s="73"/>
-      <c r="F113" s="73"/>
+      <c r="E113" s="72"/>
+      <c r="F113" s="72"/>
       <c r="H113" s="3"/>
       <c r="I113" s="3"/>
       <c r="J113" s="3"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="B114" s="73"/>
-      <c r="C114" s="148"/>
-      <c r="D114" s="148"/>
-      <c r="E114" s="73"/>
-      <c r="F114" s="73"/>
+      <c r="B114" s="72"/>
+      <c r="C114" s="146"/>
+      <c r="D114" s="146"/>
+      <c r="E114" s="72"/>
+      <c r="F114" s="72"/>
       <c r="H114" s="3"/>
       <c r="I114" s="3"/>
       <c r="J114" s="3"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="B115" s="73"/>
-      <c r="C115" s="148"/>
-      <c r="D115" s="148"/>
-      <c r="E115" s="73"/>
-      <c r="F115" s="73"/>
+      <c r="B115" s="72"/>
+      <c r="C115" s="146"/>
+      <c r="D115" s="146"/>
+      <c r="E115" s="72"/>
+      <c r="F115" s="72"/>
       <c r="H115" s="3"/>
       <c r="I115" s="3"/>
       <c r="J115" s="3"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="B116" s="73"/>
-      <c r="C116" s="148"/>
-      <c r="D116" s="148"/>
-      <c r="E116" s="73"/>
-      <c r="F116" s="73"/>
+      <c r="B116" s="72"/>
+      <c r="C116" s="146"/>
+      <c r="D116" s="146"/>
+      <c r="E116" s="72"/>
+      <c r="F116" s="72"/>
       <c r="H116" s="3"/>
       <c r="I116" s="3"/>
       <c r="J116" s="3"/>
@@ -5113,8 +5107,8 @@
     <row r="117" ht="15.75" customHeight="1">
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
-      <c r="E117" s="73"/>
-      <c r="F117" s="73"/>
+      <c r="E117" s="72"/>
+      <c r="F117" s="72"/>
       <c r="H117" s="3"/>
       <c r="I117" s="3"/>
       <c r="J117" s="3"/>
@@ -5122,361 +5116,361 @@
     <row r="118" ht="15.75" customHeight="1">
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
-      <c r="E118" s="73"/>
-      <c r="F118" s="73"/>
+      <c r="E118" s="72"/>
+      <c r="F118" s="72"/>
       <c r="H118" s="3"/>
       <c r="I118" s="3"/>
       <c r="J118" s="3"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="B119" s="73"/>
-      <c r="C119" s="148"/>
-      <c r="D119" s="148"/>
-      <c r="E119" s="73"/>
-      <c r="F119" s="73"/>
+      <c r="B119" s="72"/>
+      <c r="C119" s="146"/>
+      <c r="D119" s="146"/>
+      <c r="E119" s="72"/>
+      <c r="F119" s="72"/>
       <c r="H119" s="3"/>
       <c r="I119" s="3"/>
       <c r="J119" s="3"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="B120" s="73"/>
-      <c r="C120" s="148"/>
-      <c r="D120" s="148"/>
-      <c r="E120" s="73"/>
-      <c r="F120" s="73"/>
+      <c r="B120" s="72"/>
+      <c r="C120" s="146"/>
+      <c r="D120" s="146"/>
+      <c r="E120" s="72"/>
+      <c r="F120" s="72"/>
       <c r="H120" s="3"/>
       <c r="I120" s="3"/>
       <c r="J120" s="3"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="B121" s="73"/>
-      <c r="C121" s="148"/>
-      <c r="D121" s="148"/>
-      <c r="E121" s="73"/>
-      <c r="F121" s="73"/>
+      <c r="B121" s="72"/>
+      <c r="C121" s="146"/>
+      <c r="D121" s="146"/>
+      <c r="E121" s="72"/>
+      <c r="F121" s="72"/>
       <c r="H121" s="3"/>
       <c r="I121" s="3"/>
       <c r="J121" s="3"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="B122" s="73"/>
-      <c r="C122" s="148"/>
-      <c r="D122" s="148"/>
-      <c r="E122" s="73"/>
-      <c r="F122" s="73"/>
+      <c r="B122" s="72"/>
+      <c r="C122" s="146"/>
+      <c r="D122" s="146"/>
+      <c r="E122" s="72"/>
+      <c r="F122" s="72"/>
       <c r="H122" s="3"/>
       <c r="I122" s="3"/>
       <c r="J122" s="3"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="B123" s="73"/>
-      <c r="C123" s="148"/>
-      <c r="D123" s="148"/>
-      <c r="E123" s="73"/>
-      <c r="F123" s="73"/>
+      <c r="B123" s="72"/>
+      <c r="C123" s="146"/>
+      <c r="D123" s="146"/>
+      <c r="E123" s="72"/>
+      <c r="F123" s="72"/>
       <c r="H123" s="3"/>
       <c r="I123" s="3"/>
       <c r="J123" s="3"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="B124" s="73"/>
-      <c r="C124" s="148"/>
-      <c r="D124" s="148"/>
-      <c r="E124" s="73"/>
-      <c r="F124" s="73"/>
+      <c r="B124" s="72"/>
+      <c r="C124" s="146"/>
+      <c r="D124" s="146"/>
+      <c r="E124" s="72"/>
+      <c r="F124" s="72"/>
       <c r="H124" s="3"/>
       <c r="I124" s="3"/>
       <c r="J124" s="3"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="B125" s="73"/>
-      <c r="C125" s="148"/>
-      <c r="D125" s="148"/>
-      <c r="E125" s="73"/>
-      <c r="F125" s="73"/>
+      <c r="B125" s="72"/>
+      <c r="C125" s="146"/>
+      <c r="D125" s="146"/>
+      <c r="E125" s="72"/>
+      <c r="F125" s="72"/>
       <c r="H125" s="3"/>
       <c r="I125" s="3"/>
       <c r="J125" s="3"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="B126" s="73"/>
-      <c r="C126" s="148"/>
-      <c r="D126" s="148"/>
-      <c r="E126" s="73"/>
-      <c r="F126" s="73"/>
+      <c r="B126" s="72"/>
+      <c r="C126" s="146"/>
+      <c r="D126" s="146"/>
+      <c r="E126" s="72"/>
+      <c r="F126" s="72"/>
       <c r="H126" s="3"/>
       <c r="I126" s="3"/>
       <c r="J126" s="3"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="B127" s="73"/>
-      <c r="C127" s="148"/>
-      <c r="D127" s="148"/>
-      <c r="E127" s="73"/>
-      <c r="F127" s="73"/>
+      <c r="B127" s="72"/>
+      <c r="C127" s="146"/>
+      <c r="D127" s="146"/>
+      <c r="E127" s="72"/>
+      <c r="F127" s="72"/>
       <c r="H127" s="3"/>
       <c r="I127" s="3"/>
       <c r="J127" s="3"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="B128" s="73"/>
-      <c r="C128" s="148"/>
-      <c r="D128" s="148"/>
-      <c r="E128" s="73"/>
-      <c r="F128" s="73"/>
+      <c r="B128" s="72"/>
+      <c r="C128" s="146"/>
+      <c r="D128" s="146"/>
+      <c r="E128" s="72"/>
+      <c r="F128" s="72"/>
       <c r="H128" s="3"/>
       <c r="I128" s="3"/>
       <c r="J128" s="3"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="B129" s="73"/>
-      <c r="C129" s="148"/>
-      <c r="D129" s="148"/>
-      <c r="E129" s="73"/>
-      <c r="F129" s="73"/>
+      <c r="B129" s="72"/>
+      <c r="C129" s="146"/>
+      <c r="D129" s="146"/>
+      <c r="E129" s="72"/>
+      <c r="F129" s="72"/>
       <c r="H129" s="3"/>
       <c r="I129" s="3"/>
       <c r="J129" s="3"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="B130" s="73"/>
-      <c r="C130" s="148"/>
-      <c r="D130" s="148"/>
-      <c r="E130" s="73"/>
-      <c r="F130" s="73"/>
+      <c r="B130" s="72"/>
+      <c r="C130" s="146"/>
+      <c r="D130" s="146"/>
+      <c r="E130" s="72"/>
+      <c r="F130" s="72"/>
       <c r="H130" s="3"/>
       <c r="I130" s="3"/>
       <c r="J130" s="3"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="B131" s="73"/>
-      <c r="C131" s="148"/>
-      <c r="D131" s="148"/>
-      <c r="E131" s="73"/>
-      <c r="F131" s="73"/>
+      <c r="B131" s="72"/>
+      <c r="C131" s="146"/>
+      <c r="D131" s="146"/>
+      <c r="E131" s="72"/>
+      <c r="F131" s="72"/>
       <c r="H131" s="3"/>
       <c r="I131" s="3"/>
       <c r="J131" s="3"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="B132" s="73"/>
-      <c r="C132" s="148"/>
-      <c r="D132" s="148"/>
-      <c r="E132" s="73"/>
-      <c r="F132" s="73"/>
+      <c r="B132" s="72"/>
+      <c r="C132" s="146"/>
+      <c r="D132" s="146"/>
+      <c r="E132" s="72"/>
+      <c r="F132" s="72"/>
       <c r="H132" s="3"/>
       <c r="I132" s="3"/>
       <c r="J132" s="3"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="B133" s="73"/>
-      <c r="C133" s="148"/>
-      <c r="D133" s="148"/>
-      <c r="E133" s="73"/>
-      <c r="F133" s="73"/>
+      <c r="B133" s="72"/>
+      <c r="C133" s="146"/>
+      <c r="D133" s="146"/>
+      <c r="E133" s="72"/>
+      <c r="F133" s="72"/>
       <c r="H133" s="3"/>
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="B134" s="73"/>
-      <c r="C134" s="148"/>
-      <c r="D134" s="148"/>
-      <c r="E134" s="73"/>
-      <c r="F134" s="73"/>
+      <c r="B134" s="72"/>
+      <c r="C134" s="146"/>
+      <c r="D134" s="146"/>
+      <c r="E134" s="72"/>
+      <c r="F134" s="72"/>
       <c r="H134" s="3"/>
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="B135" s="73"/>
-      <c r="C135" s="148"/>
-      <c r="D135" s="148"/>
-      <c r="E135" s="73"/>
-      <c r="F135" s="73"/>
+      <c r="B135" s="72"/>
+      <c r="C135" s="146"/>
+      <c r="D135" s="146"/>
+      <c r="E135" s="72"/>
+      <c r="F135" s="72"/>
       <c r="H135" s="3"/>
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="B136" s="73"/>
-      <c r="C136" s="148"/>
-      <c r="D136" s="148"/>
-      <c r="E136" s="73"/>
-      <c r="F136" s="73"/>
+      <c r="B136" s="72"/>
+      <c r="C136" s="146"/>
+      <c r="D136" s="146"/>
+      <c r="E136" s="72"/>
+      <c r="F136" s="72"/>
       <c r="H136" s="3"/>
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="B137" s="73"/>
-      <c r="C137" s="148"/>
-      <c r="D137" s="148"/>
-      <c r="E137" s="73"/>
-      <c r="F137" s="73"/>
+      <c r="B137" s="72"/>
+      <c r="C137" s="146"/>
+      <c r="D137" s="146"/>
+      <c r="E137" s="72"/>
+      <c r="F137" s="72"/>
       <c r="H137" s="3"/>
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="B138" s="73"/>
-      <c r="C138" s="148"/>
-      <c r="D138" s="148"/>
-      <c r="E138" s="73"/>
+      <c r="B138" s="72"/>
+      <c r="C138" s="146"/>
+      <c r="D138" s="146"/>
+      <c r="E138" s="72"/>
       <c r="H138" s="3"/>
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="B139" s="73"/>
-      <c r="C139" s="148"/>
-      <c r="D139" s="148"/>
+      <c r="B139" s="72"/>
+      <c r="C139" s="146"/>
+      <c r="D139" s="146"/>
       <c r="H139" s="3"/>
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="B140" s="73"/>
-      <c r="C140" s="148"/>
-      <c r="D140" s="148"/>
+      <c r="B140" s="72"/>
+      <c r="C140" s="146"/>
+      <c r="D140" s="146"/>
       <c r="H140" s="3"/>
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="B141" s="73"/>
-      <c r="C141" s="148"/>
-      <c r="D141" s="148"/>
+      <c r="B141" s="72"/>
+      <c r="C141" s="146"/>
+      <c r="D141" s="146"/>
       <c r="H141" s="3"/>
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="B142" s="73"/>
-      <c r="C142" s="148"/>
-      <c r="D142" s="148"/>
-      <c r="E142" s="73"/>
-      <c r="F142" s="73"/>
+      <c r="B142" s="72"/>
+      <c r="C142" s="146"/>
+      <c r="D142" s="146"/>
+      <c r="E142" s="72"/>
+      <c r="F142" s="72"/>
       <c r="H142" s="3"/>
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="B143" s="73"/>
-      <c r="C143" s="148"/>
-      <c r="D143" s="148"/>
-      <c r="E143" s="73"/>
-      <c r="F143" s="73"/>
+      <c r="B143" s="72"/>
+      <c r="C143" s="146"/>
+      <c r="D143" s="146"/>
+      <c r="E143" s="72"/>
+      <c r="F143" s="72"/>
       <c r="H143" s="3"/>
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="B144" s="73"/>
-      <c r="C144" s="148"/>
-      <c r="D144" s="148"/>
-      <c r="E144" s="73"/>
-      <c r="F144" s="73"/>
+      <c r="B144" s="72"/>
+      <c r="C144" s="146"/>
+      <c r="D144" s="146"/>
+      <c r="E144" s="72"/>
+      <c r="F144" s="72"/>
       <c r="H144" s="3"/>
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="B145" s="73"/>
-      <c r="C145" s="148"/>
-      <c r="D145" s="148"/>
-      <c r="E145" s="73"/>
-      <c r="F145" s="73"/>
+      <c r="B145" s="72"/>
+      <c r="C145" s="146"/>
+      <c r="D145" s="146"/>
+      <c r="E145" s="72"/>
+      <c r="F145" s="72"/>
       <c r="H145" s="3"/>
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="B146" s="73"/>
-      <c r="C146" s="148"/>
-      <c r="D146" s="148"/>
-      <c r="E146" s="73"/>
-      <c r="F146" s="73"/>
+      <c r="B146" s="72"/>
+      <c r="C146" s="146"/>
+      <c r="D146" s="146"/>
+      <c r="E146" s="72"/>
+      <c r="F146" s="72"/>
       <c r="H146" s="3"/>
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="B147" s="73"/>
-      <c r="C147" s="148"/>
-      <c r="D147" s="148"/>
-      <c r="E147" s="73"/>
-      <c r="F147" s="73"/>
+      <c r="B147" s="72"/>
+      <c r="C147" s="146"/>
+      <c r="D147" s="146"/>
+      <c r="E147" s="72"/>
+      <c r="F147" s="72"/>
       <c r="H147" s="3"/>
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="B148" s="73"/>
-      <c r="C148" s="148"/>
-      <c r="D148" s="148"/>
-      <c r="E148" s="73"/>
-      <c r="F148" s="73"/>
+      <c r="B148" s="72"/>
+      <c r="C148" s="146"/>
+      <c r="D148" s="146"/>
+      <c r="E148" s="72"/>
+      <c r="F148" s="72"/>
       <c r="H148" s="3"/>
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="B149" s="73"/>
-      <c r="C149" s="148"/>
-      <c r="D149" s="148"/>
-      <c r="E149" s="73"/>
-      <c r="F149" s="73"/>
+      <c r="B149" s="72"/>
+      <c r="C149" s="146"/>
+      <c r="D149" s="146"/>
+      <c r="E149" s="72"/>
+      <c r="F149" s="72"/>
       <c r="H149" s="3"/>
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="B150" s="73"/>
-      <c r="C150" s="148"/>
-      <c r="D150" s="148"/>
-      <c r="E150" s="73"/>
-      <c r="F150" s="73"/>
+      <c r="B150" s="72"/>
+      <c r="C150" s="146"/>
+      <c r="D150" s="146"/>
+      <c r="E150" s="72"/>
+      <c r="F150" s="72"/>
       <c r="H150" s="3"/>
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="B151" s="73"/>
-      <c r="C151" s="148"/>
-      <c r="D151" s="148"/>
-      <c r="E151" s="73"/>
-      <c r="F151" s="73"/>
+      <c r="B151" s="72"/>
+      <c r="C151" s="146"/>
+      <c r="D151" s="146"/>
+      <c r="E151" s="72"/>
+      <c r="F151" s="72"/>
       <c r="H151" s="3"/>
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="B152" s="73"/>
-      <c r="C152" s="148"/>
-      <c r="D152" s="148"/>
-      <c r="E152" s="73"/>
-      <c r="F152" s="73"/>
+      <c r="B152" s="72"/>
+      <c r="C152" s="146"/>
+      <c r="D152" s="146"/>
+      <c r="E152" s="72"/>
+      <c r="F152" s="72"/>
       <c r="H152" s="3"/>
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="B153" s="73"/>
-      <c r="C153" s="148"/>
-      <c r="D153" s="148"/>
-      <c r="E153" s="73"/>
-      <c r="F153" s="73"/>
+      <c r="B153" s="72"/>
+      <c r="C153" s="146"/>
+      <c r="D153" s="146"/>
+      <c r="E153" s="72"/>
+      <c r="F153" s="72"/>
       <c r="H153" s="3"/>
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="B154" s="73"/>
-      <c r="C154" s="148"/>
-      <c r="D154" s="148"/>
-      <c r="E154" s="73"/>
-      <c r="F154" s="73"/>
+      <c r="B154" s="72"/>
+      <c r="C154" s="146"/>
+      <c r="D154" s="146"/>
+      <c r="E154" s="72"/>
+      <c r="F154" s="72"/>
       <c r="H154" s="3"/>
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
